--- a/demo_data/sectors/perakende_eticaret/sales_ledger.xlsx
+++ b/demo_data/sectors/perakende_eticaret/sales_ledger.xlsx
@@ -470,12 +470,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Maliyet</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Net Satış Tutarı</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Maliyet</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -492,7 +492,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -504,25 +504,25 @@
         <v>45658</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>4200</v>
       </c>
       <c r="F2" t="n">
-        <v>185182.48</v>
+        <v>22699.93</v>
       </c>
       <c r="G2" t="n">
-        <v>14814.6</v>
+        <v>334.03</v>
       </c>
       <c r="H2" t="n">
-        <v>170367.88</v>
+        <v>15133.21</v>
       </c>
       <c r="I2" t="n">
-        <v>123454.99</v>
+        <v>22365.9</v>
       </c>
       <c r="J2" t="n">
-        <v>170367.88</v>
+        <v>22365.9</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -531,37 +531,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F3" t="n">
-        <v>5731.84</v>
+        <v>277442.25</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>6125.33</v>
       </c>
       <c r="H3" t="n">
-        <v>5731.84</v>
+        <v>176554.16</v>
       </c>
       <c r="I3" t="n">
-        <v>3880.01</v>
+        <v>271316.92</v>
       </c>
       <c r="J3" t="n">
-        <v>5731.84</v>
+        <v>271316.92</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -570,37 +570,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>45662</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F4" t="n">
-        <v>24073.72</v>
+        <v>25942.65</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>572.76</v>
       </c>
       <c r="H4" t="n">
-        <v>24073.72</v>
+        <v>16214.16</v>
       </c>
       <c r="I4" t="n">
-        <v>16296.06</v>
+        <v>25369.89</v>
       </c>
       <c r="J4" t="n">
-        <v>24073.72</v>
+        <v>25369.89</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -621,25 +621,25 @@
         <v>45664</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>21500</v>
       </c>
       <c r="F5" t="n">
-        <v>872121.3</v>
+        <v>77467.64</v>
       </c>
       <c r="G5" t="n">
-        <v>43606.07</v>
+        <v>1140.21</v>
       </c>
       <c r="H5" t="n">
-        <v>828515.24</v>
+        <v>51164.68</v>
       </c>
       <c r="I5" t="n">
-        <v>576005.7</v>
+        <v>76327.42999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>828515.24</v>
+        <v>76327.42999999999</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -648,37 +648,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F6" t="n">
-        <v>78482.10000000001</v>
+        <v>38913.98</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>78482.10000000001</v>
+        <v>24321.24</v>
       </c>
       <c r="I6" t="n">
-        <v>52027.46</v>
+        <v>38913.98</v>
       </c>
       <c r="J6" t="n">
-        <v>78482.10000000001</v>
+        <v>38913.98</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -687,37 +687,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>45668</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F7" t="n">
-        <v>75836.63</v>
+        <v>51885.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2275.1</v>
+        <v>1909.2</v>
       </c>
       <c r="H7" t="n">
-        <v>73561.53999999999</v>
+        <v>32428.32</v>
       </c>
       <c r="I7" t="n">
-        <v>50087.45</v>
+        <v>49976.1</v>
       </c>
       <c r="J7" t="n">
-        <v>73561.53999999999</v>
+        <v>49976.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -726,37 +726,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F8" t="n">
-        <v>22839.17</v>
+        <v>16034</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>22839.17</v>
+        <v>10629.28</v>
       </c>
       <c r="I8" t="n">
-        <v>15431.87</v>
+        <v>16034</v>
       </c>
       <c r="J8" t="n">
-        <v>22839.17</v>
+        <v>16034</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -765,37 +765,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F9" t="n">
-        <v>461721.65</v>
+        <v>77467.64</v>
       </c>
       <c r="G9" t="n">
-        <v>23086.08</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>438635.57</v>
+        <v>51164.68</v>
       </c>
       <c r="I9" t="n">
-        <v>293822.87</v>
+        <v>77467.64</v>
       </c>
       <c r="J9" t="n">
-        <v>438635.57</v>
+        <v>77467.64</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -804,37 +804,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F10" t="n">
-        <v>341264.86</v>
+        <v>54047.19</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>795.5</v>
       </c>
       <c r="H10" t="n">
-        <v>341264.86</v>
+        <v>36932.25</v>
       </c>
       <c r="I10" t="n">
-        <v>225393.53</v>
+        <v>53251.69</v>
       </c>
       <c r="J10" t="n">
-        <v>341264.86</v>
+        <v>53251.69</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -843,37 +843,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F11" t="n">
-        <v>21163.71</v>
+        <v>82151.73</v>
       </c>
       <c r="G11" t="n">
-        <v>634.91</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>20528.8</v>
+        <v>51344.83</v>
       </c>
       <c r="I11" t="n">
-        <v>14461.87</v>
+        <v>82151.73</v>
       </c>
       <c r="J11" t="n">
-        <v>20528.8</v>
+        <v>82151.73</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -882,37 +882,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F12" t="n">
-        <v>68517.52</v>
+        <v>352748.01</v>
       </c>
       <c r="G12" t="n">
-        <v>2055.53</v>
+        <v>7787.93</v>
       </c>
       <c r="H12" t="n">
-        <v>66461.99000000001</v>
+        <v>233844.18</v>
       </c>
       <c r="I12" t="n">
-        <v>46295.62</v>
+        <v>344960.08</v>
       </c>
       <c r="J12" t="n">
-        <v>66461.99000000001</v>
+        <v>344960.08</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -921,37 +921,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F13" t="n">
-        <v>88887.59</v>
+        <v>17565.34</v>
       </c>
       <c r="G13" t="n">
-        <v>4444.38</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>84443.21000000001</v>
+        <v>11890.38</v>
       </c>
       <c r="I13" t="n">
-        <v>59258.39</v>
+        <v>17565.34</v>
       </c>
       <c r="J13" t="n">
-        <v>84443.21000000001</v>
+        <v>17565.34</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -960,37 +960,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>45682</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F14" t="n">
-        <v>101585.82</v>
+        <v>272578</v>
       </c>
       <c r="G14" t="n">
-        <v>5079.29</v>
+        <v>4011.96</v>
       </c>
       <c r="H14" t="n">
-        <v>96506.53</v>
+        <v>180697.78</v>
       </c>
       <c r="I14" t="n">
-        <v>63491.14</v>
+        <v>268566.04</v>
       </c>
       <c r="J14" t="n">
-        <v>96506.53</v>
+        <v>268566.04</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -999,37 +999,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F15" t="n">
-        <v>46560.17</v>
+        <v>24591.47</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>361.95</v>
       </c>
       <c r="H15" t="n">
-        <v>46560.17</v>
+        <v>16646.54</v>
       </c>
       <c r="I15" t="n">
-        <v>29100.1</v>
+        <v>24229.52</v>
       </c>
       <c r="J15" t="n">
-        <v>46560.17</v>
+        <v>24229.52</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1038,37 +1038,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F16" t="n">
-        <v>455019.81</v>
+        <v>7566.61</v>
       </c>
       <c r="G16" t="n">
-        <v>36401.58</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>418618.22</v>
+        <v>5044.4</v>
       </c>
       <c r="I16" t="n">
-        <v>300524.71</v>
+        <v>7566.61</v>
       </c>
       <c r="J16" t="n">
-        <v>418618.22</v>
+        <v>7566.61</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1077,37 +1077,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F17" t="n">
-        <v>177775.18</v>
+        <v>77827.96000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>8888.76</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>168886.42</v>
+        <v>48642.47</v>
       </c>
       <c r="I17" t="n">
-        <v>118516.79</v>
+        <v>77827.96000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>168886.42</v>
+        <v>77827.96000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1116,37 +1116,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E18" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F18" t="n">
-        <v>84654.85000000001</v>
+        <v>638117.1800000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>14088.27</v>
       </c>
       <c r="H18" t="n">
-        <v>84654.85000000001</v>
+        <v>406074.57</v>
       </c>
       <c r="I18" t="n">
-        <v>52909.28</v>
+        <v>624028.91</v>
       </c>
       <c r="J18" t="n">
-        <v>84654.85000000001</v>
+        <v>624028.91</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1167,25 +1167,25 @@
         <v>45692</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
         <v>15400</v>
       </c>
       <c r="F19" t="n">
-        <v>298761.07</v>
+        <v>638117.1800000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>14088.27</v>
       </c>
       <c r="H19" t="n">
-        <v>298761.07</v>
+        <v>406074.57</v>
       </c>
       <c r="I19" t="n">
-        <v>190120.68</v>
+        <v>624028.91</v>
       </c>
       <c r="J19" t="n">
-        <v>298761.07</v>
+        <v>624028.91</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1194,37 +1194,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F20" t="n">
-        <v>25220.09</v>
+        <v>37833.03</v>
       </c>
       <c r="G20" t="n">
-        <v>756.6</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>24463.49</v>
+        <v>25222.02</v>
       </c>
       <c r="I20" t="n">
-        <v>17072.06</v>
+        <v>37833.03</v>
       </c>
       <c r="J20" t="n">
-        <v>24463.49</v>
+        <v>37833.03</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1233,37 +1233,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F21" t="n">
-        <v>758366.35</v>
+        <v>368782.01</v>
       </c>
       <c r="G21" t="n">
-        <v>91003.96000000001</v>
+        <v>8141.92</v>
       </c>
       <c r="H21" t="n">
-        <v>667362.39</v>
+        <v>244473.46</v>
       </c>
       <c r="I21" t="n">
-        <v>500874.52</v>
+        <v>360640.09</v>
       </c>
       <c r="J21" t="n">
-        <v>667362.39</v>
+        <v>360640.09</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1272,37 +1272,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="D22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F22" t="n">
-        <v>361017.65</v>
+        <v>25762.49</v>
       </c>
       <c r="G22" t="n">
-        <v>18050.88</v>
+        <v>379.19</v>
       </c>
       <c r="H22" t="n">
-        <v>342966.77</v>
+        <v>17439.23</v>
       </c>
       <c r="I22" t="n">
-        <v>239326.31</v>
+        <v>25383.3</v>
       </c>
       <c r="J22" t="n">
-        <v>342966.77</v>
+        <v>25383.3</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,37 +1311,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F23" t="n">
-        <v>75836.63</v>
+        <v>136198.92</v>
       </c>
       <c r="G23" t="n">
-        <v>9100.4</v>
+        <v>5011.64</v>
       </c>
       <c r="H23" t="n">
-        <v>66736.24000000001</v>
+        <v>90799.28</v>
       </c>
       <c r="I23" t="n">
-        <v>50087.45</v>
+        <v>131187.28</v>
       </c>
       <c r="J23" t="n">
-        <v>66736.24000000001</v>
+        <v>131187.28</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,37 +1350,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F24" t="n">
-        <v>22927.35</v>
+        <v>166465.35</v>
       </c>
       <c r="G24" t="n">
-        <v>1146.37</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>21780.99</v>
+        <v>105932.5</v>
       </c>
       <c r="I24" t="n">
-        <v>15520.06</v>
+        <v>166465.35</v>
       </c>
       <c r="J24" t="n">
-        <v>21780.99</v>
+        <v>166465.35</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,37 +1389,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F25" t="n">
-        <v>9788.219999999999</v>
+        <v>19907.38</v>
       </c>
       <c r="G25" t="n">
-        <v>1174.59</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>8613.629999999999</v>
+        <v>13475.77</v>
       </c>
       <c r="I25" t="n">
-        <v>6613.66</v>
+        <v>19907.38</v>
       </c>
       <c r="J25" t="n">
-        <v>8613.629999999999</v>
+        <v>19907.38</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1428,37 +1428,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F26" t="n">
-        <v>50792.91</v>
+        <v>10809.44</v>
       </c>
       <c r="G26" t="n">
-        <v>4063.43</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>46729.48</v>
+        <v>7386.45</v>
       </c>
       <c r="I26" t="n">
-        <v>31745.57</v>
+        <v>10809.44</v>
       </c>
       <c r="J26" t="n">
-        <v>46729.48</v>
+        <v>10809.44</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -1482,22 +1482,22 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F27" t="n">
-        <v>15696.42</v>
+        <v>38733.82</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>570.11</v>
       </c>
       <c r="H27" t="n">
-        <v>15696.42</v>
+        <v>25582.34</v>
       </c>
       <c r="I27" t="n">
-        <v>10405.49</v>
+        <v>38163.71</v>
       </c>
       <c r="J27" t="n">
-        <v>15696.42</v>
+        <v>38163.71</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1506,37 +1506,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E28" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F28" t="n">
-        <v>75836.63</v>
+        <v>17565.34</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>646.34</v>
       </c>
       <c r="H28" t="n">
-        <v>75836.63</v>
+        <v>11890.38</v>
       </c>
       <c r="I28" t="n">
-        <v>50087.45</v>
+        <v>16919</v>
       </c>
       <c r="J28" t="n">
-        <v>75836.63</v>
+        <v>16919</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1545,37 +1545,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F29" t="n">
-        <v>52909.28</v>
+        <v>22699.82</v>
       </c>
       <c r="G29" t="n">
-        <v>6349.11</v>
+        <v>334.11</v>
       </c>
       <c r="H29" t="n">
-        <v>46560.17</v>
+        <v>15133.21</v>
       </c>
       <c r="I29" t="n">
-        <v>36154.67</v>
+        <v>22365.71</v>
       </c>
       <c r="J29" t="n">
-        <v>46560.17</v>
+        <v>22365.71</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1584,37 +1584,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F30" t="n">
-        <v>14902.78</v>
+        <v>658474.96</v>
       </c>
       <c r="G30" t="n">
-        <v>1192.22</v>
+        <v>14537.73</v>
       </c>
       <c r="H30" t="n">
-        <v>13710.56</v>
+        <v>434899.74</v>
       </c>
       <c r="I30" t="n">
-        <v>10088.04</v>
+        <v>643937.23</v>
       </c>
       <c r="J30" t="n">
-        <v>13710.56</v>
+        <v>643937.23</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1623,37 +1623,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F31" t="n">
-        <v>345321.24</v>
+        <v>82151.73</v>
       </c>
       <c r="G31" t="n">
-        <v>17266.06</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>328055.17</v>
+        <v>51344.83</v>
       </c>
       <c r="I31" t="n">
-        <v>228920.82</v>
+        <v>82151.73</v>
       </c>
       <c r="J31" t="n">
-        <v>328055.17</v>
+        <v>82151.73</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1662,7 +1662,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1674,25 +1674,25 @@
         <v>45718</v>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E32" t="n">
         <v>650</v>
       </c>
       <c r="F32" t="n">
-        <v>17195.52</v>
+        <v>24591.47</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>17195.52</v>
+        <v>16646.54</v>
       </c>
       <c r="I32" t="n">
-        <v>11640.04</v>
+        <v>24591.47</v>
       </c>
       <c r="J32" t="n">
-        <v>17195.52</v>
+        <v>24591.47</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1701,37 +1701,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E33" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F33" t="n">
-        <v>266839.14</v>
+        <v>852144.0600000001</v>
       </c>
       <c r="G33" t="n">
-        <v>8005.17</v>
+        <v>31355.88</v>
       </c>
       <c r="H33" t="n">
-        <v>258833.96</v>
+        <v>562811.4300000001</v>
       </c>
       <c r="I33" t="n">
-        <v>176893.36</v>
+        <v>820788.1800000001</v>
       </c>
       <c r="J33" t="n">
-        <v>258833.96</v>
+        <v>820788.1800000001</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1740,37 +1740,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="D34" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E34" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F34" t="n">
-        <v>24073.72</v>
+        <v>400850.01</v>
       </c>
       <c r="G34" t="n">
-        <v>722.21</v>
+        <v>14749.86</v>
       </c>
       <c r="H34" t="n">
-        <v>23351.51</v>
+        <v>265732.03</v>
       </c>
       <c r="I34" t="n">
-        <v>16296.06</v>
+        <v>386100.15</v>
       </c>
       <c r="J34" t="n">
-        <v>23351.51</v>
+        <v>386100.15</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1779,37 +1779,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E35" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F35" t="n">
-        <v>7407.3</v>
+        <v>400850.01</v>
       </c>
       <c r="G35" t="n">
-        <v>888.88</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>6518.42</v>
+        <v>265732.03</v>
       </c>
       <c r="I35" t="n">
-        <v>4938.2</v>
+        <v>400850.01</v>
       </c>
       <c r="J35" t="n">
-        <v>6518.42</v>
+        <v>400850.01</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1818,37 +1818,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="D36" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F36" t="n">
-        <v>644611.4</v>
+        <v>13331.64</v>
       </c>
       <c r="G36" t="n">
-        <v>32230.57</v>
+        <v>490.56</v>
       </c>
       <c r="H36" t="n">
-        <v>612380.83</v>
+        <v>9007.870000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>425743.34</v>
+        <v>12841.08</v>
       </c>
       <c r="J36" t="n">
-        <v>612380.83</v>
+        <v>12841.08</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1857,37 +1857,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F37" t="n">
-        <v>66665.69</v>
+        <v>166465.35</v>
       </c>
       <c r="G37" t="n">
-        <v>1999.97</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>64665.72</v>
+        <v>105932.5</v>
       </c>
       <c r="I37" t="n">
-        <v>44443.8</v>
+        <v>166465.35</v>
       </c>
       <c r="J37" t="n">
-        <v>64665.72</v>
+        <v>166465.35</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1896,37 +1896,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F38" t="n">
-        <v>265428.22</v>
+        <v>25942.65</v>
       </c>
       <c r="G38" t="n">
-        <v>21234.26</v>
+        <v>954.6</v>
       </c>
       <c r="H38" t="n">
-        <v>244193.96</v>
+        <v>17727.48</v>
       </c>
       <c r="I38" t="n">
-        <v>175306.08</v>
+        <v>24988.05</v>
       </c>
       <c r="J38" t="n">
-        <v>244193.96</v>
+        <v>24988.05</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1935,37 +1935,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>45732</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F39" t="n">
-        <v>265428.22</v>
+        <v>83232.67999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1225.07</v>
       </c>
       <c r="H39" t="n">
-        <v>265428.22</v>
+        <v>52966.25</v>
       </c>
       <c r="I39" t="n">
-        <v>175306.08</v>
+        <v>82007.61</v>
       </c>
       <c r="J39" t="n">
-        <v>265428.22</v>
+        <v>82007.61</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1974,37 +1974,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="D40" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F40" t="n">
-        <v>111109.49</v>
+        <v>138721.13</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2041.78</v>
       </c>
       <c r="H40" t="n">
-        <v>111109.49</v>
+        <v>88277.08</v>
       </c>
       <c r="I40" t="n">
-        <v>74072.99000000001</v>
+        <v>136679.35</v>
       </c>
       <c r="J40" t="n">
-        <v>111109.49</v>
+        <v>136679.35</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2013,37 +2013,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E41" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F41" t="n">
-        <v>113754.95</v>
+        <v>128632.32</v>
       </c>
       <c r="G41" t="n">
-        <v>13650.59</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>100104.36</v>
+        <v>85754.88</v>
       </c>
       <c r="I41" t="n">
-        <v>75131.17999999999</v>
+        <v>128632.32</v>
       </c>
       <c r="J41" t="n">
-        <v>100104.36</v>
+        <v>128632.32</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2052,37 +2052,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>45738</v>
       </c>
       <c r="D42" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F42" t="n">
-        <v>25220.09</v>
+        <v>96204</v>
       </c>
       <c r="G42" t="n">
-        <v>756.6</v>
+        <v>3539.97</v>
       </c>
       <c r="H42" t="n">
-        <v>24463.49</v>
+        <v>63775.69</v>
       </c>
       <c r="I42" t="n">
-        <v>17072.06</v>
+        <v>92664.03</v>
       </c>
       <c r="J42" t="n">
-        <v>24463.49</v>
+        <v>92664.03</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E43" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F43" t="n">
-        <v>133331.39</v>
+        <v>22249.43</v>
       </c>
       <c r="G43" t="n">
-        <v>10666.51</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>122664.88</v>
+        <v>15061.15</v>
       </c>
       <c r="I43" t="n">
-        <v>88887.59</v>
+        <v>22249.43</v>
       </c>
       <c r="J43" t="n">
-        <v>122664.88</v>
+        <v>22249.43</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2130,37 +2130,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>15400</v>
+        <v>1850</v>
       </c>
       <c r="F44" t="n">
-        <v>162960.58</v>
+        <v>9998.73</v>
       </c>
       <c r="G44" t="n">
-        <v>19555.27</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>143405.31</v>
+        <v>6755.9</v>
       </c>
       <c r="I44" t="n">
-        <v>103702.19</v>
+        <v>9998.73</v>
       </c>
       <c r="J44" t="n">
-        <v>143405.31</v>
+        <v>9998.73</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2169,37 +2169,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E45" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F45" t="n">
-        <v>188357.04</v>
+        <v>582628.73</v>
       </c>
       <c r="G45" t="n">
-        <v>15068.56</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>173288.47</v>
+        <v>370763.74</v>
       </c>
       <c r="I45" t="n">
-        <v>124865.9</v>
+        <v>582628.73</v>
       </c>
       <c r="J45" t="n">
-        <v>173288.47</v>
+        <v>582628.73</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2208,37 +2208,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E46" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F46" t="n">
-        <v>51851.09</v>
+        <v>86475.50999999999</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>51851.09</v>
+        <v>54047.19</v>
       </c>
       <c r="I46" t="n">
-        <v>34567.4</v>
+        <v>86475.50999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>51851.09</v>
+        <v>86475.50999999999</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2247,37 +2247,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E47" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F47" t="n">
-        <v>37918.32</v>
+        <v>582628.73</v>
       </c>
       <c r="G47" t="n">
-        <v>1137.55</v>
+        <v>8575.469999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>36780.77</v>
+        <v>370763.74</v>
       </c>
       <c r="I47" t="n">
-        <v>25043.73</v>
+        <v>574053.26</v>
       </c>
       <c r="J47" t="n">
-        <v>36780.77</v>
+        <v>574053.26</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2286,37 +2286,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="D48" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E48" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F48" t="n">
-        <v>17195.52</v>
+        <v>47561.53</v>
       </c>
       <c r="G48" t="n">
-        <v>1375.64</v>
+        <v>1050.06</v>
       </c>
       <c r="H48" t="n">
-        <v>15819.87</v>
+        <v>32500.38</v>
       </c>
       <c r="I48" t="n">
-        <v>11640.04</v>
+        <v>46511.47</v>
       </c>
       <c r="J48" t="n">
-        <v>15819.87</v>
+        <v>46511.47</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2325,12 +2325,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -2340,22 +2340,22 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4200</v>
+        <v>21500</v>
       </c>
       <c r="F49" t="n">
-        <v>22221.9</v>
+        <v>116201.46</v>
       </c>
       <c r="G49" t="n">
-        <v>666.66</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>21555.24</v>
+        <v>76747.00999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>14814.6</v>
+        <v>116201.46</v>
       </c>
       <c r="J49" t="n">
-        <v>21555.24</v>
+        <v>116201.46</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2376,25 +2376,25 @@
         <v>45755</v>
       </c>
       <c r="D50" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E50" t="n">
         <v>21500</v>
       </c>
       <c r="F50" t="n">
-        <v>644611.4</v>
+        <v>542273.49</v>
       </c>
       <c r="G50" t="n">
-        <v>32230.57</v>
+        <v>11972.24</v>
       </c>
       <c r="H50" t="n">
-        <v>612380.83</v>
+        <v>358152.73</v>
       </c>
       <c r="I50" t="n">
-        <v>425743.34</v>
+        <v>530301.25</v>
       </c>
       <c r="J50" t="n">
-        <v>612380.83</v>
+        <v>530301.25</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2403,37 +2403,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="D51" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E51" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F51" t="n">
-        <v>80422.11</v>
+        <v>23780.76</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>875.05</v>
       </c>
       <c r="H51" t="n">
-        <v>80422.11</v>
+        <v>16250.19</v>
       </c>
       <c r="I51" t="n">
-        <v>50263.82</v>
+        <v>22905.71</v>
       </c>
       <c r="J51" t="n">
-        <v>80422.11</v>
+        <v>22905.71</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2454,25 +2454,25 @@
         <v>45759</v>
       </c>
       <c r="D52" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E52" t="n">
         <v>650</v>
       </c>
       <c r="F52" t="n">
-        <v>24073.72</v>
+        <v>26933.52</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>396.42</v>
       </c>
       <c r="H52" t="n">
-        <v>24073.72</v>
+        <v>18231.92</v>
       </c>
       <c r="I52" t="n">
-        <v>16296.06</v>
+        <v>26537.1</v>
       </c>
       <c r="J52" t="n">
-        <v>24073.72</v>
+        <v>26537.1</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2481,37 +2481,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="D53" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E53" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F53" t="n">
-        <v>834202.98</v>
+        <v>15223.29</v>
       </c>
       <c r="G53" t="n">
-        <v>66736.24000000001</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>767466.75</v>
+        <v>10305</v>
       </c>
       <c r="I53" t="n">
-        <v>550961.97</v>
+        <v>15223.29</v>
       </c>
       <c r="J53" t="n">
-        <v>767466.75</v>
+        <v>15223.29</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2520,37 +2520,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D54" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E54" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F54" t="n">
-        <v>392410.49</v>
+        <v>19907.38</v>
       </c>
       <c r="G54" t="n">
-        <v>31392.84</v>
+        <v>732.52</v>
       </c>
       <c r="H54" t="n">
-        <v>361017.65</v>
+        <v>13475.77</v>
       </c>
       <c r="I54" t="n">
-        <v>260137.29</v>
+        <v>19174.86</v>
       </c>
       <c r="J54" t="n">
-        <v>361017.65</v>
+        <v>19174.86</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2559,37 +2559,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D55" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E55" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F55" t="n">
-        <v>392410.49</v>
+        <v>9368.18</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>206.83</v>
       </c>
       <c r="H55" t="n">
-        <v>392410.49</v>
+        <v>6341.54</v>
       </c>
       <c r="I55" t="n">
-        <v>260137.29</v>
+        <v>9161.35</v>
       </c>
       <c r="J55" t="n">
-        <v>392410.49</v>
+        <v>9161.35</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2598,37 +2598,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v>45767</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E56" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F56" t="n">
-        <v>13050.96</v>
+        <v>416163.38</v>
       </c>
       <c r="G56" t="n">
-        <v>1044.08</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>12006.88</v>
+        <v>264831.24</v>
       </c>
       <c r="I56" t="n">
-        <v>8818.209999999999</v>
+        <v>416163.38</v>
       </c>
       <c r="J56" t="n">
-        <v>12006.88</v>
+        <v>416163.38</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2642,32 +2642,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>15400</v>
+        <v>4200</v>
       </c>
       <c r="F57" t="n">
-        <v>162960.58</v>
+        <v>15133.21</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>222.74</v>
       </c>
       <c r="H57" t="n">
-        <v>162960.58</v>
+        <v>10088.81</v>
       </c>
       <c r="I57" t="n">
-        <v>103702.19</v>
+        <v>14910.47</v>
       </c>
       <c r="J57" t="n">
-        <v>162960.58</v>
+        <v>14910.47</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2676,37 +2676,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D58" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F58" t="n">
-        <v>25396.45</v>
+        <v>34590.2</v>
       </c>
       <c r="G58" t="n">
-        <v>2031.72</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>23364.74</v>
+        <v>21618.88</v>
       </c>
       <c r="I58" t="n">
-        <v>17354.24</v>
+        <v>34590.2</v>
       </c>
       <c r="J58" t="n">
-        <v>23364.74</v>
+        <v>34590.2</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2715,37 +2715,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E59" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F59" t="n">
-        <v>81480.28999999999</v>
+        <v>22249.43</v>
       </c>
       <c r="G59" t="n">
-        <v>2444.41</v>
+        <v>327.48</v>
       </c>
       <c r="H59" t="n">
-        <v>79035.88</v>
+        <v>15061.15</v>
       </c>
       <c r="I59" t="n">
-        <v>51851.09</v>
+        <v>21921.95</v>
       </c>
       <c r="J59" t="n">
-        <v>79035.88</v>
+        <v>21921.95</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2759,32 +2759,32 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E60" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F60" t="n">
-        <v>135800.49</v>
+        <v>256544</v>
       </c>
       <c r="G60" t="n">
-        <v>16296.06</v>
+        <v>9439.91</v>
       </c>
       <c r="H60" t="n">
-        <v>119504.43</v>
+        <v>170068.5</v>
       </c>
       <c r="I60" t="n">
-        <v>86418.49000000001</v>
+        <v>247104.09</v>
       </c>
       <c r="J60" t="n">
-        <v>119504.43</v>
+        <v>247104.09</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2793,37 +2793,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D61" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E61" t="n">
-        <v>4200</v>
+        <v>21500</v>
       </c>
       <c r="F61" t="n">
-        <v>125924.09</v>
+        <v>387338.21</v>
       </c>
       <c r="G61" t="n">
-        <v>15110.89</v>
+        <v>8551.6</v>
       </c>
       <c r="H61" t="n">
-        <v>110813.2</v>
+        <v>255823.38</v>
       </c>
       <c r="I61" t="n">
-        <v>83949.39</v>
+        <v>378786.61</v>
       </c>
       <c r="J61" t="n">
-        <v>110813.2</v>
+        <v>378786.61</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2832,37 +2832,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D62" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E62" t="n">
-        <v>8900</v>
+        <v>4200</v>
       </c>
       <c r="F62" t="n">
-        <v>94178.52</v>
+        <v>98365.89</v>
       </c>
       <c r="G62" t="n">
-        <v>11301.42</v>
+        <v>3619.52</v>
       </c>
       <c r="H62" t="n">
-        <v>82877.10000000001</v>
+        <v>65577.25999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>62432.95</v>
+        <v>94746.37</v>
       </c>
       <c r="J62" t="n">
-        <v>82877.10000000001</v>
+        <v>94746.37</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2871,37 +2871,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v>45781</v>
       </c>
       <c r="D63" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E63" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F63" t="n">
-        <v>21780.99</v>
+        <v>15133.21</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>556.85</v>
       </c>
       <c r="H63" t="n">
-        <v>21780.99</v>
+        <v>10341.03</v>
       </c>
       <c r="I63" t="n">
-        <v>14744.05</v>
+        <v>14576.36</v>
       </c>
       <c r="J63" t="n">
-        <v>21780.99</v>
+        <v>14576.36</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2910,7 +2910,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2922,25 +2922,25 @@
         <v>45783</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
         <v>1850</v>
       </c>
       <c r="F64" t="n">
-        <v>9788.219999999999</v>
+        <v>6665.82</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>98.11</v>
       </c>
       <c r="H64" t="n">
-        <v>9788.219999999999</v>
+        <v>4503.93</v>
       </c>
       <c r="I64" t="n">
-        <v>6613.66</v>
+        <v>6567.71</v>
       </c>
       <c r="J64" t="n">
-        <v>9788.219999999999</v>
+        <v>6567.71</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2949,37 +2949,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D65" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E65" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F65" t="n">
-        <v>570362.04</v>
+        <v>387338.21</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>14252.67</v>
       </c>
       <c r="H65" t="n">
-        <v>570362.04</v>
+        <v>255823.38</v>
       </c>
       <c r="I65" t="n">
-        <v>362957.66</v>
+        <v>373085.54</v>
       </c>
       <c r="J65" t="n">
-        <v>570362.04</v>
+        <v>373085.54</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2988,37 +2988,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>45787</v>
       </c>
       <c r="D66" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E66" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F66" t="n">
-        <v>84654.85000000001</v>
+        <v>105932.5</v>
       </c>
       <c r="G66" t="n">
-        <v>10158.58</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>74496.27</v>
+        <v>70621.66</v>
       </c>
       <c r="I66" t="n">
-        <v>52909.28</v>
+        <v>105932.5</v>
       </c>
       <c r="J66" t="n">
-        <v>74496.27</v>
+        <v>105932.5</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3027,37 +3027,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D67" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E67" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F67" t="n">
-        <v>796284.67</v>
+        <v>665861.4</v>
       </c>
       <c r="G67" t="n">
-        <v>63702.77</v>
+        <v>9800.540000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>732581.89</v>
+        <v>423729.98</v>
       </c>
       <c r="I67" t="n">
-        <v>525918.24</v>
+        <v>656060.86</v>
       </c>
       <c r="J67" t="n">
-        <v>732581.89</v>
+        <v>656060.86</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3066,37 +3066,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="D68" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E68" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F68" t="n">
-        <v>434561.55</v>
+        <v>51885.3</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>434561.55</v>
+        <v>32428.32</v>
       </c>
       <c r="I68" t="n">
-        <v>276539.17</v>
+        <v>51885.3</v>
       </c>
       <c r="J68" t="n">
-        <v>434561.55</v>
+        <v>51885.3</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3105,37 +3105,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="D69" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E69" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F69" t="n">
-        <v>42327.42</v>
+        <v>63325.29</v>
       </c>
       <c r="G69" t="n">
-        <v>2116.37</v>
+        <v>2330.15</v>
       </c>
       <c r="H69" t="n">
-        <v>40211.05</v>
+        <v>42787.36</v>
       </c>
       <c r="I69" t="n">
-        <v>26454.64</v>
+        <v>60995.14</v>
       </c>
       <c r="J69" t="n">
-        <v>40211.05</v>
+        <v>60995.14</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3144,37 +3144,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v>45795</v>
       </c>
       <c r="D70" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E70" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F70" t="n">
-        <v>19576.43</v>
+        <v>21078.4</v>
       </c>
       <c r="G70" t="n">
-        <v>978.8200000000001</v>
+        <v>310.24</v>
       </c>
       <c r="H70" t="n">
-        <v>18597.61</v>
+        <v>14268.46</v>
       </c>
       <c r="I70" t="n">
-        <v>13227.32</v>
+        <v>20768.16</v>
       </c>
       <c r="J70" t="n">
-        <v>18597.61</v>
+        <v>20768.16</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3183,37 +3183,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D71" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E71" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F71" t="n">
-        <v>568774.76</v>
+        <v>73504.17999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1622.82</v>
       </c>
       <c r="H71" t="n">
-        <v>568774.76</v>
+        <v>45940.11</v>
       </c>
       <c r="I71" t="n">
-        <v>375655.89</v>
+        <v>71881.36</v>
       </c>
       <c r="J71" t="n">
-        <v>568774.76</v>
+        <v>71881.36</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3222,37 +3222,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D72" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E72" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F72" t="n">
-        <v>172660.62</v>
+        <v>554884.5</v>
       </c>
       <c r="G72" t="n">
-        <v>20719.27</v>
+        <v>20417.78</v>
       </c>
       <c r="H72" t="n">
-        <v>151941.34</v>
+        <v>353108.32</v>
       </c>
       <c r="I72" t="n">
-        <v>114460.41</v>
+        <v>534466.72</v>
       </c>
       <c r="J72" t="n">
-        <v>151941.34</v>
+        <v>534466.72</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3261,37 +3261,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v>45801</v>
       </c>
       <c r="D73" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E73" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F73" t="n">
-        <v>14902.78</v>
+        <v>64136</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1415.99</v>
       </c>
       <c r="H73" t="n">
-        <v>14902.78</v>
+        <v>42517.12</v>
       </c>
       <c r="I73" t="n">
-        <v>10088.04</v>
+        <v>62720.01</v>
       </c>
       <c r="J73" t="n">
-        <v>14902.78</v>
+        <v>62720.01</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3312,25 +3312,25 @@
         <v>45803</v>
       </c>
       <c r="D74" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E74" t="n">
         <v>650</v>
       </c>
       <c r="F74" t="n">
-        <v>19488.25</v>
+        <v>21078.4</v>
       </c>
       <c r="G74" t="n">
-        <v>1559.06</v>
+        <v>310.24</v>
       </c>
       <c r="H74" t="n">
-        <v>17929.19</v>
+        <v>14268.46</v>
       </c>
       <c r="I74" t="n">
-        <v>13192.05</v>
+        <v>20768.16</v>
       </c>
       <c r="J74" t="n">
-        <v>17929.19</v>
+        <v>20768.16</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3339,37 +3339,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F75" t="n">
-        <v>9170.940000000001</v>
+        <v>112238</v>
       </c>
       <c r="G75" t="n">
-        <v>458.55</v>
+        <v>4129.96</v>
       </c>
       <c r="H75" t="n">
-        <v>8712.389999999999</v>
+        <v>74404.97</v>
       </c>
       <c r="I75" t="n">
-        <v>6208.02</v>
+        <v>108108.04</v>
       </c>
       <c r="J75" t="n">
-        <v>8712.389999999999</v>
+        <v>108108.04</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3378,37 +3378,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D76" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E76" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F76" t="n">
-        <v>407401.46</v>
+        <v>73504.17999999999</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>407401.46</v>
+        <v>45940.11</v>
       </c>
       <c r="I76" t="n">
-        <v>259255.47</v>
+        <v>73504.17999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>407401.46</v>
+        <v>73504.17999999999</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3417,37 +3417,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F77" t="n">
-        <v>14814.6</v>
+        <v>16664.55</v>
       </c>
       <c r="G77" t="n">
-        <v>444.44</v>
+        <v>245.28</v>
       </c>
       <c r="H77" t="n">
-        <v>14370.16</v>
+        <v>11259.83</v>
       </c>
       <c r="I77" t="n">
-        <v>9876.4</v>
+        <v>16419.27</v>
       </c>
       <c r="J77" t="n">
-        <v>14370.16</v>
+        <v>16419.27</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3456,37 +3456,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E78" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F78" t="n">
-        <v>33861.94</v>
+        <v>658474.96</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>14537.73</v>
       </c>
       <c r="H78" t="n">
-        <v>33861.94</v>
+        <v>434899.74</v>
       </c>
       <c r="I78" t="n">
-        <v>21163.71</v>
+        <v>643937.23</v>
       </c>
       <c r="J78" t="n">
-        <v>33861.94</v>
+        <v>643937.23</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3495,37 +3495,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D79" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E79" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F79" t="n">
-        <v>21780.99</v>
+        <v>176374</v>
       </c>
       <c r="G79" t="n">
-        <v>2613.72</v>
+        <v>6489.94</v>
       </c>
       <c r="H79" t="n">
-        <v>19167.27</v>
+        <v>116922.09</v>
       </c>
       <c r="I79" t="n">
-        <v>14744.05</v>
+        <v>169884.06</v>
       </c>
       <c r="J79" t="n">
-        <v>19167.27</v>
+        <v>169884.06</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="D80" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E80" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F80" t="n">
-        <v>52909.28</v>
+        <v>208442</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>7669.93</v>
       </c>
       <c r="H80" t="n">
-        <v>52909.28</v>
+        <v>138180.65</v>
       </c>
       <c r="I80" t="n">
-        <v>36154.67</v>
+        <v>200772.07</v>
       </c>
       <c r="J80" t="n">
-        <v>52909.28</v>
+        <v>200772.07</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3573,37 +3573,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="D81" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E81" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F81" t="n">
-        <v>606693.08</v>
+        <v>527140.28</v>
       </c>
       <c r="G81" t="n">
-        <v>18200.79</v>
+        <v>7758.76</v>
       </c>
       <c r="H81" t="n">
-        <v>588492.29</v>
+        <v>335452.9</v>
       </c>
       <c r="I81" t="n">
-        <v>400699.62</v>
+        <v>519381.52</v>
       </c>
       <c r="J81" t="n">
-        <v>588492.29</v>
+        <v>519381.52</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3612,37 +3612,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E82" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F82" t="n">
-        <v>9788.219999999999</v>
+        <v>890877.88</v>
       </c>
       <c r="G82" t="n">
-        <v>489.41</v>
+        <v>32781.15</v>
       </c>
       <c r="H82" t="n">
-        <v>9298.809999999999</v>
+        <v>588393.76</v>
       </c>
       <c r="I82" t="n">
-        <v>6613.66</v>
+        <v>858096.73</v>
       </c>
       <c r="J82" t="n">
-        <v>9298.809999999999</v>
+        <v>858096.73</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3651,7 +3651,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3663,25 +3663,25 @@
         <v>45821</v>
       </c>
       <c r="D83" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
         <v>21500</v>
       </c>
       <c r="F83" t="n">
-        <v>303346.54</v>
+        <v>38733.82</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>570.11</v>
       </c>
       <c r="H83" t="n">
-        <v>303346.54</v>
+        <v>25582.34</v>
       </c>
       <c r="I83" t="n">
-        <v>200349.81</v>
+        <v>38163.71</v>
       </c>
       <c r="J83" t="n">
-        <v>303346.54</v>
+        <v>38163.71</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3690,37 +3690,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E84" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F84" t="n">
-        <v>2292.74</v>
+        <v>105932.5</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>3897.94</v>
       </c>
       <c r="H84" t="n">
-        <v>2292.74</v>
+        <v>70621.66</v>
       </c>
       <c r="I84" t="n">
-        <v>1552.01</v>
+        <v>102034.56</v>
       </c>
       <c r="J84" t="n">
-        <v>2292.74</v>
+        <v>102034.56</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -3744,22 +3744,22 @@
         <v>20</v>
       </c>
       <c r="E85" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F85" t="n">
-        <v>758366.35</v>
+        <v>66658.2</v>
       </c>
       <c r="G85" t="n">
-        <v>91003.96000000001</v>
+        <v>1471.67</v>
       </c>
       <c r="H85" t="n">
-        <v>667362.39</v>
+        <v>45039.33</v>
       </c>
       <c r="I85" t="n">
-        <v>500874.52</v>
+        <v>65186.53</v>
       </c>
       <c r="J85" t="n">
-        <v>667362.39</v>
+        <v>65186.53</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3768,37 +3768,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="D86" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E86" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F86" t="n">
-        <v>379183.17</v>
+        <v>51885.3</v>
       </c>
       <c r="G86" t="n">
-        <v>30334.65</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>348848.52</v>
+        <v>35454.96</v>
       </c>
       <c r="I86" t="n">
-        <v>250437.26</v>
+        <v>51885.3</v>
       </c>
       <c r="J86" t="n">
-        <v>348848.52</v>
+        <v>51885.3</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3807,37 +3807,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="D87" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E87" t="n">
-        <v>4200</v>
+        <v>21500</v>
       </c>
       <c r="F87" t="n">
-        <v>103702.19</v>
+        <v>232402.93</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>8551.6</v>
       </c>
       <c r="H87" t="n">
-        <v>103702.19</v>
+        <v>153494.03</v>
       </c>
       <c r="I87" t="n">
-        <v>69134.78999999999</v>
+        <v>223851.33</v>
       </c>
       <c r="J87" t="n">
-        <v>103702.19</v>
+        <v>223851.33</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3846,37 +3846,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D88" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F88" t="n">
-        <v>651842.33</v>
+        <v>21618.88</v>
       </c>
       <c r="G88" t="n">
-        <v>19555.27</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>632287.0600000001</v>
+        <v>13511.8</v>
       </c>
       <c r="I88" t="n">
-        <v>414808.76</v>
+        <v>21618.88</v>
       </c>
       <c r="J88" t="n">
-        <v>632287.0600000001</v>
+        <v>21618.88</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3885,37 +3885,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="D89" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E89" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="F89" t="n">
-        <v>50792.91</v>
+        <v>52966.25</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>50792.91</v>
+        <v>35310.83</v>
       </c>
       <c r="I89" t="n">
-        <v>31745.57</v>
+        <v>52966.25</v>
       </c>
       <c r="J89" t="n">
-        <v>50792.91</v>
+        <v>52966.25</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3924,37 +3924,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="D90" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E90" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F90" t="n">
-        <v>61992.04</v>
+        <v>16394.31</v>
       </c>
       <c r="G90" t="n">
-        <v>4959.36</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>57032.68</v>
+        <v>11097.69</v>
       </c>
       <c r="I90" t="n">
-        <v>41886.51</v>
+        <v>16394.31</v>
       </c>
       <c r="J90" t="n">
-        <v>57032.68</v>
+        <v>16394.31</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="D91" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E91" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F91" t="n">
-        <v>20634.62</v>
+        <v>30266.43</v>
       </c>
       <c r="G91" t="n">
-        <v>619.04</v>
+        <v>1113.7</v>
       </c>
       <c r="H91" t="n">
-        <v>20015.58</v>
+        <v>20682.06</v>
       </c>
       <c r="I91" t="n">
-        <v>13968.05</v>
+        <v>29152.73</v>
       </c>
       <c r="J91" t="n">
-        <v>20015.58</v>
+        <v>29152.73</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4002,37 +4002,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="D92" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E92" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F92" t="n">
-        <v>71956.62</v>
+        <v>929611.7</v>
       </c>
       <c r="G92" t="n">
-        <v>3597.83</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>68358.78999999999</v>
+        <v>613976.1</v>
       </c>
       <c r="I92" t="n">
-        <v>44972.89</v>
+        <v>929611.7</v>
       </c>
       <c r="J92" t="n">
-        <v>68358.78999999999</v>
+        <v>929611.7</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4041,37 +4041,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="D93" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E93" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F93" t="n">
-        <v>543201.9399999999</v>
+        <v>272578</v>
       </c>
       <c r="G93" t="n">
-        <v>65184.23</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>478017.71</v>
+        <v>180697.78</v>
       </c>
       <c r="I93" t="n">
-        <v>345673.96</v>
+        <v>272578</v>
       </c>
       <c r="J93" t="n">
-        <v>478017.71</v>
+        <v>272578</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4080,37 +4080,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E94" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F94" t="n">
-        <v>37036.5</v>
+        <v>25762.49</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>568.78</v>
       </c>
       <c r="H94" t="n">
-        <v>37036.5</v>
+        <v>17439.23</v>
       </c>
       <c r="I94" t="n">
-        <v>24691</v>
+        <v>25193.71</v>
       </c>
       <c r="J94" t="n">
-        <v>37036.5</v>
+        <v>25193.71</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4119,12 +4119,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
@@ -4134,22 +4134,22 @@
         <v>11</v>
       </c>
       <c r="E95" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F95" t="n">
-        <v>12610.05</v>
+        <v>47561.53</v>
       </c>
       <c r="G95" t="n">
-        <v>1008.8</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>11601.24</v>
+        <v>29725.96</v>
       </c>
       <c r="I95" t="n">
-        <v>8536.030000000001</v>
+        <v>47561.53</v>
       </c>
       <c r="J95" t="n">
-        <v>11601.24</v>
+        <v>47561.53</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4158,37 +4158,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E96" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F96" t="n">
-        <v>109874.94</v>
+        <v>21078.4</v>
       </c>
       <c r="G96" t="n">
-        <v>8790</v>
+        <v>310.24</v>
       </c>
       <c r="H96" t="n">
-        <v>101084.94</v>
+        <v>14268.46</v>
       </c>
       <c r="I96" t="n">
-        <v>72838.44</v>
+        <v>20768.16</v>
       </c>
       <c r="J96" t="n">
-        <v>101084.94</v>
+        <v>20768.16</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4197,37 +4197,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="D97" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E97" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F97" t="n">
-        <v>71956.62</v>
+        <v>554884.5</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>12250.67</v>
       </c>
       <c r="H97" t="n">
-        <v>71956.62</v>
+        <v>353108.32</v>
       </c>
       <c r="I97" t="n">
-        <v>44972.89</v>
+        <v>542633.83</v>
       </c>
       <c r="J97" t="n">
-        <v>71956.62</v>
+        <v>542633.83</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4236,37 +4236,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E98" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F98" t="n">
-        <v>16313.69</v>
+        <v>19456.99</v>
       </c>
       <c r="G98" t="n">
-        <v>1957.64</v>
+        <v>715.95</v>
       </c>
       <c r="H98" t="n">
-        <v>14356.05</v>
+        <v>13295.61</v>
       </c>
       <c r="I98" t="n">
-        <v>11022.77</v>
+        <v>18741.04</v>
       </c>
       <c r="J98" t="n">
-        <v>14356.05</v>
+        <v>18741.04</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4275,37 +4275,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="D99" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E99" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F99" t="n">
-        <v>644611.4</v>
+        <v>21618.88</v>
       </c>
       <c r="G99" t="n">
-        <v>32230.57</v>
+        <v>318.2</v>
       </c>
       <c r="H99" t="n">
-        <v>612380.83</v>
+        <v>14772.9</v>
       </c>
       <c r="I99" t="n">
-        <v>425743.34</v>
+        <v>21300.68</v>
       </c>
       <c r="J99" t="n">
-        <v>612380.83</v>
+        <v>21300.68</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4314,37 +4314,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D100" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E100" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F100" t="n">
-        <v>172660.62</v>
+        <v>49723.42</v>
       </c>
       <c r="G100" t="n">
-        <v>13812.85</v>
+        <v>1097.79</v>
       </c>
       <c r="H100" t="n">
-        <v>158847.77</v>
+        <v>33977.67</v>
       </c>
       <c r="I100" t="n">
-        <v>114460.41</v>
+        <v>48625.63</v>
       </c>
       <c r="J100" t="n">
-        <v>158847.77</v>
+        <v>48625.63</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4358,32 +4358,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>45858</v>
       </c>
       <c r="D101" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E101" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F101" t="n">
-        <v>204053.46</v>
+        <v>464805.85</v>
       </c>
       <c r="G101" t="n">
-        <v>16324.28</v>
+        <v>17103.21</v>
       </c>
       <c r="H101" t="n">
-        <v>187729.18</v>
+        <v>306988.05</v>
       </c>
       <c r="I101" t="n">
-        <v>135271.39</v>
+        <v>447702.64</v>
       </c>
       <c r="J101" t="n">
-        <v>187729.18</v>
+        <v>447702.64</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4404,25 +4404,25 @@
         <v>45860</v>
       </c>
       <c r="D102" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E102" t="n">
         <v>15400</v>
       </c>
       <c r="F102" t="n">
-        <v>516041.85</v>
+        <v>277442.25</v>
       </c>
       <c r="G102" t="n">
-        <v>15481.26</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>500560.59</v>
+        <v>176554.16</v>
       </c>
       <c r="I102" t="n">
-        <v>328390.27</v>
+        <v>277442.25</v>
       </c>
       <c r="J102" t="n">
-        <v>500560.59</v>
+        <v>277442.25</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4431,37 +4431,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D103" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E103" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F103" t="n">
-        <v>872121.3</v>
+        <v>56209.08</v>
       </c>
       <c r="G103" t="n">
-        <v>69769.7</v>
+        <v>827.3200000000001</v>
       </c>
       <c r="H103" t="n">
-        <v>802351.6</v>
+        <v>35130.67</v>
       </c>
       <c r="I103" t="n">
-        <v>576005.7</v>
+        <v>55381.76</v>
       </c>
       <c r="J103" t="n">
-        <v>802351.6</v>
+        <v>55381.76</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4470,37 +4470,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E104" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F104" t="n">
-        <v>37918.32</v>
+        <v>160340</v>
       </c>
       <c r="G104" t="n">
-        <v>1137.55</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>36780.77</v>
+        <v>106292.81</v>
       </c>
       <c r="I104" t="n">
-        <v>25043.73</v>
+        <v>160340</v>
       </c>
       <c r="J104" t="n">
-        <v>36780.77</v>
+        <v>160340</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4509,7 +4509,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4521,25 +4521,25 @@
         <v>45866</v>
       </c>
       <c r="D105" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E105" t="n">
         <v>4200</v>
       </c>
       <c r="F105" t="n">
-        <v>103702.19</v>
+        <v>90799.28</v>
       </c>
       <c r="G105" t="n">
-        <v>8296.18</v>
+        <v>2004.65</v>
       </c>
       <c r="H105" t="n">
-        <v>95406.00999999999</v>
+        <v>60532.85</v>
       </c>
       <c r="I105" t="n">
-        <v>69134.78999999999</v>
+        <v>88794.63</v>
       </c>
       <c r="J105" t="n">
-        <v>95406.00999999999</v>
+        <v>88794.63</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4548,37 +4548,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D106" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E106" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F106" t="n">
-        <v>65254.78</v>
+        <v>665861.4</v>
       </c>
       <c r="G106" t="n">
-        <v>3262.74</v>
+        <v>14700.8</v>
       </c>
       <c r="H106" t="n">
-        <v>61992.04</v>
+        <v>423729.98</v>
       </c>
       <c r="I106" t="n">
-        <v>44091.07</v>
+        <v>651160.6</v>
       </c>
       <c r="J106" t="n">
-        <v>61992.04</v>
+        <v>651160.6</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4587,7 +4587,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4599,25 +4599,25 @@
         <v>45870</v>
       </c>
       <c r="D107" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E107" t="n">
         <v>1200</v>
       </c>
       <c r="F107" t="n">
-        <v>50792.91</v>
+        <v>38913.98</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>572.76</v>
       </c>
       <c r="H107" t="n">
-        <v>50792.91</v>
+        <v>26591.22</v>
       </c>
       <c r="I107" t="n">
-        <v>34708.49</v>
+        <v>38341.22</v>
       </c>
       <c r="J107" t="n">
-        <v>50792.91</v>
+        <v>38341.22</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4626,37 +4626,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="D108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F108" t="n">
-        <v>227509.9</v>
+        <v>138721.13</v>
       </c>
       <c r="G108" t="n">
-        <v>18200.79</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>209309.11</v>
+        <v>88277.08</v>
       </c>
       <c r="I108" t="n">
-        <v>150262.36</v>
+        <v>138721.13</v>
       </c>
       <c r="J108" t="n">
-        <v>209309.11</v>
+        <v>138721.13</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4665,37 +4665,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D109" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E109" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F109" t="n">
-        <v>21163.71</v>
+        <v>17295.1</v>
       </c>
       <c r="G109" t="n">
-        <v>2539.65</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>18624.07</v>
+        <v>11818.32</v>
       </c>
       <c r="I109" t="n">
-        <v>13227.32</v>
+        <v>17295.1</v>
       </c>
       <c r="J109" t="n">
-        <v>18624.07</v>
+        <v>17295.1</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4704,37 +4704,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D110" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E110" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F110" t="n">
-        <v>61992.04</v>
+        <v>45399.64</v>
       </c>
       <c r="G110" t="n">
-        <v>7439.04</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>54553</v>
+        <v>31023.09</v>
       </c>
       <c r="I110" t="n">
-        <v>41886.51</v>
+        <v>45399.64</v>
       </c>
       <c r="J110" t="n">
-        <v>54553</v>
+        <v>45399.64</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4743,37 +4743,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E111" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F111" t="n">
-        <v>2116.37</v>
+        <v>105932.5</v>
       </c>
       <c r="G111" t="n">
-        <v>105.82</v>
+        <v>1559.18</v>
       </c>
       <c r="H111" t="n">
-        <v>2010.55</v>
+        <v>70621.66</v>
       </c>
       <c r="I111" t="n">
-        <v>1446.19</v>
+        <v>104373.32</v>
       </c>
       <c r="J111" t="n">
-        <v>2010.55</v>
+        <v>104373.32</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4782,37 +4782,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E112" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F112" t="n">
-        <v>21163.71</v>
+        <v>154935.28</v>
       </c>
       <c r="G112" t="n">
-        <v>1058.19</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>20105.53</v>
+        <v>102329.35</v>
       </c>
       <c r="I112" t="n">
-        <v>13227.32</v>
+        <v>154935.28</v>
       </c>
       <c r="J112" t="n">
-        <v>20105.53</v>
+        <v>154935.28</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4821,12 +4821,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
@@ -4836,22 +4836,22 @@
         <v>14</v>
       </c>
       <c r="E113" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F113" t="n">
-        <v>29629.2</v>
+        <v>224476</v>
       </c>
       <c r="G113" t="n">
-        <v>2370.34</v>
+        <v>4955.95</v>
       </c>
       <c r="H113" t="n">
-        <v>27258.86</v>
+        <v>148809.94</v>
       </c>
       <c r="I113" t="n">
-        <v>20246.62</v>
+        <v>219520.05</v>
       </c>
       <c r="J113" t="n">
-        <v>27258.86</v>
+        <v>219520.05</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4860,37 +4860,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="D114" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E114" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F114" t="n">
-        <v>910039.62</v>
+        <v>54047.19</v>
       </c>
       <c r="G114" t="n">
-        <v>109204.75</v>
+        <v>795.5</v>
       </c>
       <c r="H114" t="n">
-        <v>800834.86</v>
+        <v>36932.25</v>
       </c>
       <c r="I114" t="n">
-        <v>601049.42</v>
+        <v>53251.69</v>
       </c>
       <c r="J114" t="n">
-        <v>800834.86</v>
+        <v>53251.69</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4899,37 +4899,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D115" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E115" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F115" t="n">
-        <v>266839.14</v>
+        <v>582628.73</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>266839.14</v>
+        <v>370763.74</v>
       </c>
       <c r="I115" t="n">
-        <v>176893.36</v>
+        <v>582628.73</v>
       </c>
       <c r="J115" t="n">
-        <v>266839.14</v>
+        <v>582628.73</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4938,37 +4938,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="D116" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E116" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F116" t="n">
-        <v>25220.09</v>
+        <v>158898.74</v>
       </c>
       <c r="G116" t="n">
-        <v>1261</v>
+        <v>5846.91</v>
       </c>
       <c r="H116" t="n">
-        <v>23959.09</v>
+        <v>105932.5</v>
       </c>
       <c r="I116" t="n">
-        <v>17072.06</v>
+        <v>153051.83</v>
       </c>
       <c r="J116" t="n">
-        <v>23959.09</v>
+        <v>153051.83</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4977,37 +4977,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D117" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E117" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F117" t="n">
-        <v>46560.17</v>
+        <v>19997.46</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>441.5</v>
       </c>
       <c r="H117" t="n">
-        <v>46560.17</v>
+        <v>13511.8</v>
       </c>
       <c r="I117" t="n">
-        <v>29100.1</v>
+        <v>19555.96</v>
       </c>
       <c r="J117" t="n">
-        <v>46560.17</v>
+        <v>19555.96</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5016,37 +5016,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="D118" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E118" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F118" t="n">
-        <v>20634.62</v>
+        <v>32068</v>
       </c>
       <c r="G118" t="n">
-        <v>619.04</v>
+        <v>707.99</v>
       </c>
       <c r="H118" t="n">
-        <v>20015.58</v>
+        <v>21258.56</v>
       </c>
       <c r="I118" t="n">
-        <v>13968.05</v>
+        <v>31360.01</v>
       </c>
       <c r="J118" t="n">
-        <v>20015.58</v>
+        <v>31360.01</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5055,37 +5055,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="D119" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E119" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F119" t="n">
-        <v>543201.9399999999</v>
+        <v>232402.93</v>
       </c>
       <c r="G119" t="n">
-        <v>27160.1</v>
+        <v>3420.64</v>
       </c>
       <c r="H119" t="n">
-        <v>516041.85</v>
+        <v>153494.03</v>
       </c>
       <c r="I119" t="n">
-        <v>345673.96</v>
+        <v>228982.29</v>
       </c>
       <c r="J119" t="n">
-        <v>516041.85</v>
+        <v>228982.29</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5094,37 +5094,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D120" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F120" t="n">
-        <v>19047.34</v>
+        <v>3332.91</v>
       </c>
       <c r="G120" t="n">
-        <v>1523.79</v>
+        <v>49.06</v>
       </c>
       <c r="H120" t="n">
-        <v>17523.55</v>
+        <v>2251.97</v>
       </c>
       <c r="I120" t="n">
-        <v>13015.68</v>
+        <v>3283.85</v>
       </c>
       <c r="J120" t="n">
-        <v>17523.55</v>
+        <v>3283.85</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5133,37 +5133,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E121" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F121" t="n">
-        <v>21163.71</v>
+        <v>83232.67999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>634.91</v>
+        <v>1225.07</v>
       </c>
       <c r="H121" t="n">
-        <v>20528.8</v>
+        <v>55488.45</v>
       </c>
       <c r="I121" t="n">
-        <v>14461.87</v>
+        <v>82007.61</v>
       </c>
       <c r="J121" t="n">
-        <v>20528.8</v>
+        <v>82007.61</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5172,37 +5172,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="D122" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E122" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F122" t="n">
-        <v>48676.54</v>
+        <v>193669.1</v>
       </c>
       <c r="G122" t="n">
-        <v>5841.18</v>
+        <v>7126.34</v>
       </c>
       <c r="H122" t="n">
-        <v>42835.35</v>
+        <v>127911.69</v>
       </c>
       <c r="I122" t="n">
-        <v>33262.3</v>
+        <v>186542.76</v>
       </c>
       <c r="J122" t="n">
-        <v>42835.35</v>
+        <v>186542.76</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5216,32 +5216,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="D123" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E123" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F123" t="n">
-        <v>18341.88</v>
+        <v>194209.58</v>
       </c>
       <c r="G123" t="n">
-        <v>550.26</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>17791.63</v>
+        <v>123587.91</v>
       </c>
       <c r="I123" t="n">
-        <v>12416.04</v>
+        <v>194209.58</v>
       </c>
       <c r="J123" t="n">
-        <v>17791.63</v>
+        <v>194209.58</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5250,37 +5250,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="D124" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E124" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F124" t="n">
-        <v>271600.97</v>
+        <v>384816.01</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>8495.92</v>
       </c>
       <c r="H124" t="n">
-        <v>271600.97</v>
+        <v>255102.75</v>
       </c>
       <c r="I124" t="n">
-        <v>172836.98</v>
+        <v>376320.09</v>
       </c>
       <c r="J124" t="n">
-        <v>271600.97</v>
+        <v>376320.09</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5289,37 +5289,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>45906</v>
       </c>
       <c r="D125" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E125" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F125" t="n">
-        <v>55025.65</v>
+        <v>638117.1800000001</v>
       </c>
       <c r="G125" t="n">
-        <v>1650.77</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>53374.88</v>
+        <v>406074.57</v>
       </c>
       <c r="I125" t="n">
-        <v>34391.03</v>
+        <v>638117.1800000001</v>
       </c>
       <c r="J125" t="n">
-        <v>53374.88</v>
+        <v>638117.1800000001</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5328,12 +5328,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
@@ -5343,22 +5343,22 @@
         <v>10</v>
       </c>
       <c r="E126" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F126" t="n">
-        <v>156964.2</v>
+        <v>11710.22</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>430.89</v>
       </c>
       <c r="H126" t="n">
-        <v>156964.2</v>
+        <v>7926.92</v>
       </c>
       <c r="I126" t="n">
-        <v>104054.92</v>
+        <v>11279.33</v>
       </c>
       <c r="J126" t="n">
-        <v>156964.2</v>
+        <v>11279.33</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5367,37 +5367,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D127" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E127" t="n">
-        <v>4200</v>
+        <v>1200</v>
       </c>
       <c r="F127" t="n">
-        <v>88887.59</v>
+        <v>12971.33</v>
       </c>
       <c r="G127" t="n">
-        <v>4444.38</v>
+        <v>477.3</v>
       </c>
       <c r="H127" t="n">
-        <v>84443.21000000001</v>
+        <v>8863.74</v>
       </c>
       <c r="I127" t="n">
-        <v>59258.39</v>
+        <v>12494.03</v>
       </c>
       <c r="J127" t="n">
-        <v>84443.21000000001</v>
+        <v>12494.03</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5406,37 +5406,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="D128" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E128" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F128" t="n">
-        <v>651842.33</v>
+        <v>60532.85</v>
       </c>
       <c r="G128" t="n">
-        <v>32592.12</v>
+        <v>2227.39</v>
       </c>
       <c r="H128" t="n">
-        <v>619250.21</v>
+        <v>37833.03</v>
       </c>
       <c r="I128" t="n">
-        <v>414808.76</v>
+        <v>58305.46</v>
       </c>
       <c r="J128" t="n">
-        <v>619250.21</v>
+        <v>58305.46</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5445,37 +5445,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="D129" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E129" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F129" t="n">
-        <v>38094.68</v>
+        <v>98365.89</v>
       </c>
       <c r="G129" t="n">
-        <v>1142.84</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>36951.84</v>
+        <v>65577.25999999999</v>
       </c>
       <c r="I129" t="n">
-        <v>26031.37</v>
+        <v>98365.89</v>
       </c>
       <c r="J129" t="n">
-        <v>36951.84</v>
+        <v>98365.89</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5484,37 +5484,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="D130" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E130" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F130" t="n">
-        <v>135800.49</v>
+        <v>256544</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>3775.96</v>
       </c>
       <c r="H130" t="n">
-        <v>135800.49</v>
+        <v>170068.5</v>
       </c>
       <c r="I130" t="n">
-        <v>86418.49000000001</v>
+        <v>252768.04</v>
       </c>
       <c r="J130" t="n">
-        <v>135800.49</v>
+        <v>252768.04</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5535,25 +5535,25 @@
         <v>45918</v>
       </c>
       <c r="D131" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
         <v>1200</v>
       </c>
       <c r="F131" t="n">
-        <v>16930.97</v>
+        <v>2161.89</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>31.82</v>
       </c>
       <c r="H131" t="n">
-        <v>16930.97</v>
+        <v>1477.29</v>
       </c>
       <c r="I131" t="n">
-        <v>11569.5</v>
+        <v>2130.07</v>
       </c>
       <c r="J131" t="n">
-        <v>16930.97</v>
+        <v>2130.07</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5562,7 +5562,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5574,25 +5574,25 @@
         <v>45920</v>
       </c>
       <c r="D132" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E132" t="n">
         <v>1200</v>
       </c>
       <c r="F132" t="n">
-        <v>44443.8</v>
+        <v>32428.32</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>477.3</v>
       </c>
       <c r="H132" t="n">
-        <v>44443.8</v>
+        <v>22159.35</v>
       </c>
       <c r="I132" t="n">
-        <v>30369.93</v>
+        <v>31951.02</v>
       </c>
       <c r="J132" t="n">
-        <v>44443.8</v>
+        <v>31951.02</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5601,37 +5601,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="D133" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E133" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F133" t="n">
-        <v>103702.19</v>
+        <v>527140.28</v>
       </c>
       <c r="G133" t="n">
-        <v>3111.07</v>
+        <v>19396.89</v>
       </c>
       <c r="H133" t="n">
-        <v>100591.12</v>
+        <v>335452.9</v>
       </c>
       <c r="I133" t="n">
-        <v>69134.78999999999</v>
+        <v>507743.39</v>
       </c>
       <c r="J133" t="n">
-        <v>100591.12</v>
+        <v>507743.39</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5640,37 +5640,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="D134" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E134" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F134" t="n">
-        <v>151673.27</v>
+        <v>582628.73</v>
       </c>
       <c r="G134" t="n">
-        <v>18200.79</v>
+        <v>8575.469999999999</v>
       </c>
       <c r="H134" t="n">
-        <v>133472.48</v>
+        <v>370763.74</v>
       </c>
       <c r="I134" t="n">
-        <v>100174.9</v>
+        <v>574053.26</v>
       </c>
       <c r="J134" t="n">
-        <v>133472.48</v>
+        <v>574053.26</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F135" t="n">
-        <v>15696.42</v>
+        <v>4323.78</v>
       </c>
       <c r="G135" t="n">
-        <v>1255.71</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>14440.71</v>
+        <v>2954.58</v>
       </c>
       <c r="I135" t="n">
-        <v>10405.49</v>
+        <v>4323.78</v>
       </c>
       <c r="J135" t="n">
-        <v>14440.71</v>
+        <v>4323.78</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5718,37 +5718,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v>45928</v>
       </c>
       <c r="D136" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E136" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F136" t="n">
-        <v>219749.88</v>
+        <v>166465.35</v>
       </c>
       <c r="G136" t="n">
-        <v>26369.99</v>
+        <v>3675.2</v>
       </c>
       <c r="H136" t="n">
-        <v>193379.89</v>
+        <v>105932.5</v>
       </c>
       <c r="I136" t="n">
-        <v>145676.88</v>
+        <v>162790.15</v>
       </c>
       <c r="J136" t="n">
-        <v>193379.89</v>
+        <v>162790.15</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -5757,37 +5757,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D137" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E137" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F137" t="n">
-        <v>606693.08</v>
+        <v>638117.1800000001</v>
       </c>
       <c r="G137" t="n">
-        <v>72803.17</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>533889.91</v>
+        <v>406074.57</v>
       </c>
       <c r="I137" t="n">
-        <v>400699.62</v>
+        <v>638117.1800000001</v>
       </c>
       <c r="J137" t="n">
-        <v>533889.91</v>
+        <v>638117.1800000001</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -5796,7 +5796,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5808,25 +5808,25 @@
         <v>45933</v>
       </c>
       <c r="D138" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E138" t="n">
         <v>15400</v>
       </c>
       <c r="F138" t="n">
-        <v>298761.07</v>
+        <v>332930.7</v>
       </c>
       <c r="G138" t="n">
-        <v>8962.83</v>
+        <v>12250.67</v>
       </c>
       <c r="H138" t="n">
-        <v>289798.24</v>
+        <v>211864.99</v>
       </c>
       <c r="I138" t="n">
-        <v>190120.68</v>
+        <v>320680.03</v>
       </c>
       <c r="J138" t="n">
-        <v>289798.24</v>
+        <v>320680.03</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -5835,37 +5835,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="D139" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E139" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F139" t="n">
-        <v>81568.47</v>
+        <v>10809.44</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>238.65</v>
       </c>
       <c r="H139" t="n">
-        <v>81568.47</v>
+        <v>7386.45</v>
       </c>
       <c r="I139" t="n">
-        <v>55113.83</v>
+        <v>10570.79</v>
       </c>
       <c r="J139" t="n">
-        <v>81568.47</v>
+        <v>10570.79</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -5874,37 +5874,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>45937</v>
       </c>
       <c r="D140" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E140" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F140" t="n">
-        <v>38094.68</v>
+        <v>929611.7</v>
       </c>
       <c r="G140" t="n">
-        <v>4571.36</v>
+        <v>34206.41</v>
       </c>
       <c r="H140" t="n">
-        <v>33523.32</v>
+        <v>613976.1</v>
       </c>
       <c r="I140" t="n">
-        <v>26031.37</v>
+        <v>895405.29</v>
       </c>
       <c r="J140" t="n">
-        <v>33523.32</v>
+        <v>895405.29</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -5913,37 +5913,37 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="D141" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E141" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F141" t="n">
-        <v>19576.43</v>
+        <v>99446.83</v>
       </c>
       <c r="G141" t="n">
-        <v>978.8200000000001</v>
+        <v>3659.29</v>
       </c>
       <c r="H141" t="n">
-        <v>18597.61</v>
+        <v>62154.27</v>
       </c>
       <c r="I141" t="n">
-        <v>13227.32</v>
+        <v>95787.53999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>18597.61</v>
+        <v>95787.53999999999</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="D142" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E142" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F142" t="n">
-        <v>31392.84</v>
+        <v>968345.52</v>
       </c>
       <c r="G142" t="n">
-        <v>1569.64</v>
+        <v>35631.68</v>
       </c>
       <c r="H142" t="n">
-        <v>29823.2</v>
+        <v>639558.4399999999</v>
       </c>
       <c r="I142" t="n">
-        <v>20810.98</v>
+        <v>932713.84</v>
       </c>
       <c r="J142" t="n">
-        <v>29823.2</v>
+        <v>932713.84</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -5996,32 +5996,32 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="D143" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E143" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F143" t="n">
-        <v>227509.9</v>
+        <v>54047.19</v>
       </c>
       <c r="G143" t="n">
-        <v>27301.19</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>200208.72</v>
+        <v>36932.25</v>
       </c>
       <c r="I143" t="n">
-        <v>150262.36</v>
+        <v>54047.19</v>
       </c>
       <c r="J143" t="n">
-        <v>200208.72</v>
+        <v>54047.19</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6030,37 +6030,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E144" t="n">
-        <v>15400</v>
+        <v>4200</v>
       </c>
       <c r="F144" t="n">
-        <v>54320.19</v>
+        <v>128632.32</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>2839.93</v>
       </c>
       <c r="H144" t="n">
-        <v>54320.19</v>
+        <v>85754.88</v>
       </c>
       <c r="I144" t="n">
-        <v>34567.4</v>
+        <v>125792.39</v>
       </c>
       <c r="J144" t="n">
-        <v>54320.19</v>
+        <v>125792.39</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6069,37 +6069,37 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D145" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E145" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F145" t="n">
-        <v>81480.28999999999</v>
+        <v>3513.07</v>
       </c>
       <c r="G145" t="n">
-        <v>2444.41</v>
+        <v>129.27</v>
       </c>
       <c r="H145" t="n">
-        <v>79035.88</v>
+        <v>2378.08</v>
       </c>
       <c r="I145" t="n">
-        <v>54320.19</v>
+        <v>3383.8</v>
       </c>
       <c r="J145" t="n">
-        <v>79035.88</v>
+        <v>3383.8</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6108,37 +6108,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v>45949</v>
       </c>
       <c r="D146" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E146" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F146" t="n">
-        <v>189591.59</v>
+        <v>59992.38</v>
       </c>
       <c r="G146" t="n">
-        <v>15167.33</v>
+        <v>2207.51</v>
       </c>
       <c r="H146" t="n">
-        <v>174424.26</v>
+        <v>40535.39</v>
       </c>
       <c r="I146" t="n">
-        <v>125218.63</v>
+        <v>57784.87</v>
       </c>
       <c r="J146" t="n">
-        <v>174424.26</v>
+        <v>57784.87</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6147,37 +6147,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D147" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E147" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F147" t="n">
-        <v>190120.68</v>
+        <v>96204</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>1415.99</v>
       </c>
       <c r="H147" t="n">
-        <v>190120.68</v>
+        <v>63775.69</v>
       </c>
       <c r="I147" t="n">
-        <v>120985.89</v>
+        <v>94788.00999999999</v>
       </c>
       <c r="J147" t="n">
-        <v>190120.68</v>
+        <v>94788.00999999999</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D148" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E148" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F148" t="n">
-        <v>376714.07</v>
+        <v>154935.28</v>
       </c>
       <c r="G148" t="n">
-        <v>18835.7</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>357878.37</v>
+        <v>102329.35</v>
       </c>
       <c r="I148" t="n">
-        <v>249731.8</v>
+        <v>154935.28</v>
       </c>
       <c r="J148" t="n">
-        <v>357878.37</v>
+        <v>154935.28</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -6225,37 +6225,37 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="D149" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E149" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F149" t="n">
-        <v>624682.23</v>
+        <v>116201.46</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>4275.8</v>
       </c>
       <c r="H149" t="n">
-        <v>624682.23</v>
+        <v>76747.00999999999</v>
       </c>
       <c r="I149" t="n">
-        <v>397525.06</v>
+        <v>111925.66</v>
       </c>
       <c r="J149" t="n">
-        <v>624682.23</v>
+        <v>111925.66</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -6264,37 +6264,37 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="D150" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E150" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F150" t="n">
-        <v>11463.68</v>
+        <v>49993.65</v>
       </c>
       <c r="G150" t="n">
-        <v>917.09</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>10546.58</v>
+        <v>33779.49</v>
       </c>
       <c r="I150" t="n">
-        <v>7760.03</v>
+        <v>49993.65</v>
       </c>
       <c r="J150" t="n">
-        <v>10546.58</v>
+        <v>49993.65</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -6303,37 +6303,37 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D151" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E151" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F151" t="n">
-        <v>12698.23</v>
+        <v>64856.63</v>
       </c>
       <c r="G151" t="n">
-        <v>1015.86</v>
+        <v>2386.49</v>
       </c>
       <c r="H151" t="n">
-        <v>11682.37</v>
+        <v>40535.39</v>
       </c>
       <c r="I151" t="n">
-        <v>8677.120000000001</v>
+        <v>62470.14</v>
       </c>
       <c r="J151" t="n">
-        <v>11682.37</v>
+        <v>62470.14</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -6342,37 +6342,37 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D152" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E152" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F152" t="n">
-        <v>59258.39</v>
+        <v>852144.0600000001</v>
       </c>
       <c r="G152" t="n">
-        <v>4740.67</v>
+        <v>12542.35</v>
       </c>
       <c r="H152" t="n">
-        <v>54517.72</v>
+        <v>562811.4300000001</v>
       </c>
       <c r="I152" t="n">
-        <v>37036.5</v>
+        <v>839601.71</v>
       </c>
       <c r="J152" t="n">
-        <v>54517.72</v>
+        <v>839601.71</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
@@ -6381,12 +6381,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
@@ -6396,22 +6396,22 @@
         <v>13</v>
       </c>
       <c r="E153" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F153" t="n">
-        <v>96294.89</v>
+        <v>43327.83</v>
       </c>
       <c r="G153" t="n">
-        <v>11555.39</v>
+        <v>637.72</v>
       </c>
       <c r="H153" t="n">
-        <v>84739.5</v>
+        <v>29275.56</v>
       </c>
       <c r="I153" t="n">
-        <v>64196.59</v>
+        <v>42690.11</v>
       </c>
       <c r="J153" t="n">
-        <v>84739.5</v>
+        <v>42690.11</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -6420,37 +6420,37 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D154" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E154" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F154" t="n">
-        <v>78482.10000000001</v>
+        <v>79989.84</v>
       </c>
       <c r="G154" t="n">
-        <v>3924.1</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>74557.99000000001</v>
+        <v>54047.19</v>
       </c>
       <c r="I154" t="n">
-        <v>52027.46</v>
+        <v>79989.84</v>
       </c>
       <c r="J154" t="n">
-        <v>74557.99000000001</v>
+        <v>79989.84</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -6459,37 +6459,37 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F155" t="n">
-        <v>2116.37</v>
+        <v>15133.21</v>
       </c>
       <c r="G155" t="n">
-        <v>63.49</v>
+        <v>334.11</v>
       </c>
       <c r="H155" t="n">
-        <v>2052.88</v>
+        <v>10088.81</v>
       </c>
       <c r="I155" t="n">
-        <v>1446.19</v>
+        <v>14799.1</v>
       </c>
       <c r="J155" t="n">
-        <v>2052.88</v>
+        <v>14799.1</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -6498,37 +6498,37 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v>45969</v>
       </c>
       <c r="D156" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E156" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F156" t="n">
-        <v>31745.57</v>
+        <v>136198.92</v>
       </c>
       <c r="G156" t="n">
-        <v>952.37</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>30793.2</v>
+        <v>90799.28</v>
       </c>
       <c r="I156" t="n">
-        <v>21692.8</v>
+        <v>136198.92</v>
       </c>
       <c r="J156" t="n">
-        <v>30793.2</v>
+        <v>136198.92</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -6537,37 +6537,37 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D157" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E157" t="n">
-        <v>15400</v>
+        <v>4200</v>
       </c>
       <c r="F157" t="n">
-        <v>516041.85</v>
+        <v>121065.71</v>
       </c>
       <c r="G157" t="n">
-        <v>61925.02</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>454116.82</v>
+        <v>80710.47</v>
       </c>
       <c r="I157" t="n">
-        <v>328390.27</v>
+        <v>121065.71</v>
       </c>
       <c r="J157" t="n">
-        <v>454116.82</v>
+        <v>121065.71</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -6576,37 +6576,37 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="D158" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E158" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F158" t="n">
-        <v>29364.65</v>
+        <v>25942.65</v>
       </c>
       <c r="G158" t="n">
-        <v>3523.76</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>25840.89</v>
+        <v>16214.16</v>
       </c>
       <c r="I158" t="n">
-        <v>19840.98</v>
+        <v>25942.65</v>
       </c>
       <c r="J158" t="n">
-        <v>25840.89</v>
+        <v>25942.65</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -6615,37 +6615,37 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E159" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F159" t="n">
-        <v>4232.74</v>
+        <v>51885.3</v>
       </c>
       <c r="G159" t="n">
-        <v>507.93</v>
+        <v>1145.52</v>
       </c>
       <c r="H159" t="n">
-        <v>3724.81</v>
+        <v>32428.32</v>
       </c>
       <c r="I159" t="n">
-        <v>2892.37</v>
+        <v>50739.78</v>
       </c>
       <c r="J159" t="n">
-        <v>3724.81</v>
+        <v>50739.78</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -6654,37 +6654,37 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v>45977</v>
       </c>
       <c r="D160" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E160" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F160" t="n">
-        <v>379183.17</v>
+        <v>56209.08</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>379183.17</v>
+        <v>35130.67</v>
       </c>
       <c r="I160" t="n">
-        <v>250437.26</v>
+        <v>56209.08</v>
       </c>
       <c r="J160" t="n">
-        <v>379183.17</v>
+        <v>56209.08</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -6693,37 +6693,37 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="D161" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E161" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F161" t="n">
-        <v>624682.23</v>
+        <v>336714.01</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>4955.95</v>
       </c>
       <c r="H161" t="n">
-        <v>624682.23</v>
+        <v>223214.9</v>
       </c>
       <c r="I161" t="n">
-        <v>397525.06</v>
+        <v>331758.06</v>
       </c>
       <c r="J161" t="n">
-        <v>624682.23</v>
+        <v>331758.06</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -6732,37 +6732,37 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D162" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E162" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F162" t="n">
-        <v>325921.17</v>
+        <v>288612</v>
       </c>
       <c r="G162" t="n">
-        <v>26073.69</v>
+        <v>6371.94</v>
       </c>
       <c r="H162" t="n">
-        <v>299847.47</v>
+        <v>191327.06</v>
       </c>
       <c r="I162" t="n">
-        <v>207404.38</v>
+        <v>282240.06</v>
       </c>
       <c r="J162" t="n">
-        <v>299847.47</v>
+        <v>282240.06</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -6771,37 +6771,37 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="D163" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E163" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F163" t="n">
-        <v>10581.86</v>
+        <v>384816.01</v>
       </c>
       <c r="G163" t="n">
-        <v>529.09</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>10052.76</v>
+        <v>255102.75</v>
       </c>
       <c r="I163" t="n">
-        <v>7230.93</v>
+        <v>384816.01</v>
       </c>
       <c r="J163" t="n">
-        <v>10052.76</v>
+        <v>384816.01</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -6810,37 +6810,37 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="D164" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E164" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F164" t="n">
-        <v>910039.62</v>
+        <v>83322.75</v>
       </c>
       <c r="G164" t="n">
-        <v>72803.17</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>837236.45</v>
+        <v>56299.16</v>
       </c>
       <c r="I164" t="n">
-        <v>601049.42</v>
+        <v>83322.75</v>
       </c>
       <c r="J164" t="n">
-        <v>837236.45</v>
+        <v>83322.75</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -6849,37 +6849,37 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D165" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E165" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F165" t="n">
-        <v>97353.08</v>
+        <v>852144.0600000001</v>
       </c>
       <c r="G165" t="n">
-        <v>7788.25</v>
+        <v>31355.88</v>
       </c>
       <c r="H165" t="n">
-        <v>89564.83</v>
+        <v>562811.4300000001</v>
       </c>
       <c r="I165" t="n">
-        <v>60845.67</v>
+        <v>820788.1800000001</v>
       </c>
       <c r="J165" t="n">
-        <v>89564.83</v>
+        <v>820788.1800000001</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -6888,37 +6888,37 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="D166" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E166" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F166" t="n">
-        <v>947957.9399999999</v>
+        <v>34590.2</v>
       </c>
       <c r="G166" t="n">
-        <v>75836.63</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>872121.3</v>
+        <v>21618.88</v>
       </c>
       <c r="I166" t="n">
-        <v>626093.15</v>
+        <v>34590.2</v>
       </c>
       <c r="J166" t="n">
-        <v>872121.3</v>
+        <v>34590.2</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -6927,37 +6927,37 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="D167" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E167" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F167" t="n">
-        <v>52909.28</v>
+        <v>5855.11</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="H167" t="n">
-        <v>52909.28</v>
+        <v>3963.46</v>
       </c>
       <c r="I167" t="n">
-        <v>36154.67</v>
+        <v>5768.93</v>
       </c>
       <c r="J167" t="n">
-        <v>52909.28</v>
+        <v>5768.93</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -6966,7 +6966,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6978,25 +6978,25 @@
         <v>45993</v>
       </c>
       <c r="D168" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E168" t="n">
         <v>4200</v>
       </c>
       <c r="F168" t="n">
-        <v>125924.09</v>
+        <v>15133.21</v>
       </c>
       <c r="G168" t="n">
-        <v>6296.2</v>
+        <v>334.11</v>
       </c>
       <c r="H168" t="n">
-        <v>119627.88</v>
+        <v>10088.81</v>
       </c>
       <c r="I168" t="n">
-        <v>83949.39</v>
+        <v>14799.1</v>
       </c>
       <c r="J168" t="n">
-        <v>119627.88</v>
+        <v>14799.1</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -7005,37 +7005,37 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="D169" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E169" t="n">
-        <v>650</v>
+        <v>1850</v>
       </c>
       <c r="F169" t="n">
-        <v>3439.1</v>
+        <v>26663.28</v>
       </c>
       <c r="G169" t="n">
-        <v>275.13</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>3163.97</v>
+        <v>18015.73</v>
       </c>
       <c r="I169" t="n">
-        <v>2328.01</v>
+        <v>26663.28</v>
       </c>
       <c r="J169" t="n">
-        <v>3163.97</v>
+        <v>26663.28</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -7049,32 +7049,32 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v>45997</v>
       </c>
       <c r="D170" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E170" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F170" t="n">
-        <v>58729.3</v>
+        <v>151332.14</v>
       </c>
       <c r="G170" t="n">
-        <v>4698.34</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>54030.96</v>
+        <v>100888.09</v>
       </c>
       <c r="I170" t="n">
-        <v>39681.96</v>
+        <v>151332.14</v>
       </c>
       <c r="J170" t="n">
-        <v>54030.96</v>
+        <v>151332.14</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -7083,37 +7083,37 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="D171" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E171" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F171" t="n">
-        <v>94178.52</v>
+        <v>26663.28</v>
       </c>
       <c r="G171" t="n">
-        <v>2825.36</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>91353.16</v>
+        <v>18015.73</v>
       </c>
       <c r="I171" t="n">
-        <v>62432.95</v>
+        <v>26663.28</v>
       </c>
       <c r="J171" t="n">
-        <v>91353.16</v>
+        <v>26663.28</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -7122,7 +7122,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -7134,25 +7134,25 @@
         <v>46001</v>
       </c>
       <c r="D172" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E172" t="n">
         <v>21500</v>
       </c>
       <c r="F172" t="n">
-        <v>151673.27</v>
+        <v>309870.57</v>
       </c>
       <c r="G172" t="n">
-        <v>18200.79</v>
+        <v>11402.14</v>
       </c>
       <c r="H172" t="n">
-        <v>133472.48</v>
+        <v>204658.7</v>
       </c>
       <c r="I172" t="n">
-        <v>100174.9</v>
+        <v>298468.43</v>
       </c>
       <c r="J172" t="n">
-        <v>133472.48</v>
+        <v>298468.43</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -7166,32 +7166,32 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="D173" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E173" t="n">
-        <v>21500</v>
+        <v>1850</v>
       </c>
       <c r="F173" t="n">
-        <v>113754.95</v>
+        <v>16664.55</v>
       </c>
       <c r="G173" t="n">
-        <v>9100.4</v>
+        <v>613.2</v>
       </c>
       <c r="H173" t="n">
-        <v>104654.56</v>
+        <v>11259.83</v>
       </c>
       <c r="I173" t="n">
-        <v>75131.17999999999</v>
+        <v>16051.35</v>
       </c>
       <c r="J173" t="n">
-        <v>104654.56</v>
+        <v>16051.35</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -7200,241 +7200,241 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v>46005</v>
       </c>
       <c r="D174" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E174" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F174" t="n">
-        <v>48941.08</v>
+        <v>51885.3</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>1909.2</v>
       </c>
       <c r="H174" t="n">
-        <v>48941.08</v>
+        <v>35454.96</v>
       </c>
       <c r="I174" t="n">
-        <v>33068.3</v>
+        <v>49976.1</v>
       </c>
       <c r="J174" t="n">
-        <v>24470.54</v>
+        <v>14992.83</v>
       </c>
       <c r="K174" t="n">
-        <v>24470.54</v>
+        <v>34983.27</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="D175" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E175" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F175" t="n">
-        <v>720448.03</v>
+        <v>9368.18</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>137.89</v>
       </c>
       <c r="H175" t="n">
-        <v>720448.03</v>
+        <v>6341.54</v>
       </c>
       <c r="I175" t="n">
-        <v>475830.79</v>
+        <v>9230.290000000001</v>
       </c>
       <c r="J175" t="n">
-        <v>360224.02</v>
+        <v>2769.09</v>
       </c>
       <c r="K175" t="n">
-        <v>360224.02</v>
+        <v>6461.2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D176" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E176" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F176" t="n">
-        <v>651842.33</v>
+        <v>352748.01</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>12979.88</v>
       </c>
       <c r="H176" t="n">
-        <v>651842.33</v>
+        <v>233844.18</v>
       </c>
       <c r="I176" t="n">
-        <v>414808.76</v>
+        <v>339768.13</v>
       </c>
       <c r="J176" t="n">
-        <v>195552.7</v>
+        <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>456289.63</v>
+        <v>339768.13</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="D177" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E177" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F177" t="n">
-        <v>78305.73</v>
+        <v>43237.75</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>636.4</v>
       </c>
       <c r="H177" t="n">
-        <v>78305.73</v>
+        <v>27023.6</v>
       </c>
       <c r="I177" t="n">
-        <v>52909.28</v>
+        <v>42601.35</v>
       </c>
       <c r="J177" t="n">
-        <v>39152.87</v>
+        <v>21300.67</v>
       </c>
       <c r="K177" t="n">
-        <v>39152.87</v>
+        <v>21300.68</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="D178" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E178" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F178" t="n">
-        <v>45678.35</v>
+        <v>336714.01</v>
       </c>
       <c r="G178" t="n">
-        <v>1370.35</v>
+        <v>7433.93</v>
       </c>
       <c r="H178" t="n">
-        <v>44307.99</v>
+        <v>223214.9</v>
       </c>
       <c r="I178" t="n">
-        <v>30863.75</v>
+        <v>329280.08</v>
       </c>
       <c r="J178" t="n">
-        <v>22154</v>
+        <v>98784.02</v>
       </c>
       <c r="K178" t="n">
-        <v>22154</v>
+        <v>230496.06</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="D179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E179" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F179" t="n">
-        <v>9788.219999999999</v>
+        <v>77467.64</v>
       </c>
       <c r="G179" t="n">
-        <v>489.41</v>
+        <v>1140.21</v>
       </c>
       <c r="H179" t="n">
-        <v>9298.809999999999</v>
+        <v>51164.68</v>
       </c>
       <c r="I179" t="n">
-        <v>6613.66</v>
+        <v>76327.42999999999</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>9298.809999999999</v>
+        <v>76327.42999999999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -7446,28 +7446,28 @@
         <v>46017</v>
       </c>
       <c r="D180" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E180" t="n">
         <v>2400</v>
       </c>
       <c r="F180" t="n">
-        <v>25396.45</v>
+        <v>73504.17999999999</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>1081.88</v>
       </c>
       <c r="H180" t="n">
-        <v>25396.45</v>
+        <v>45940.11</v>
       </c>
       <c r="I180" t="n">
-        <v>15872.78</v>
+        <v>72422.3</v>
       </c>
       <c r="J180" t="n">
-        <v>12698.23</v>
+        <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>12698.23</v>
+        <v>72422.3</v>
       </c>
     </row>
     <row r="181">
@@ -7485,28 +7485,28 @@
         <v>46019</v>
       </c>
       <c r="D181" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E181" t="n">
         <v>2400</v>
       </c>
       <c r="F181" t="n">
-        <v>50792.91</v>
+        <v>60532.85</v>
       </c>
       <c r="G181" t="n">
-        <v>2539.65</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>48253.26</v>
+        <v>37833.03</v>
       </c>
       <c r="I181" t="n">
-        <v>31745.57</v>
+        <v>60532.85</v>
       </c>
       <c r="J181" t="n">
-        <v>14475.98</v>
+        <v>18159.85</v>
       </c>
       <c r="K181" t="n">
-        <v>33777.28</v>
+        <v>42373</v>
       </c>
     </row>
   </sheetData>

--- a/demo_data/sectors/perakende_eticaret/sales_ledger.xlsx
+++ b/demo_data/sectors/perakende_eticaret/sales_ledger.xlsx
@@ -492,37 +492,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="F2" t="n">
-        <v>22699.93</v>
+        <v>632630.12</v>
       </c>
       <c r="G2" t="n">
-        <v>334.03</v>
+        <v>27102.11</v>
       </c>
       <c r="H2" t="n">
-        <v>15133.21</v>
+        <v>349611.38</v>
       </c>
       <c r="I2" t="n">
-        <v>22365.9</v>
+        <v>605528.01</v>
       </c>
       <c r="J2" t="n">
-        <v>22365.9</v>
+        <v>605528.01</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -531,37 +531,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F3" t="n">
-        <v>277442.25</v>
+        <v>108213.05</v>
       </c>
       <c r="G3" t="n">
-        <v>6125.33</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>176554.16</v>
+        <v>53274.11</v>
       </c>
       <c r="I3" t="n">
-        <v>271316.92</v>
+        <v>108213.05</v>
       </c>
       <c r="J3" t="n">
-        <v>271316.92</v>
+        <v>108213.05</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -570,37 +570,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>45662</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F4" t="n">
-        <v>25942.65</v>
+        <v>8324.08</v>
       </c>
       <c r="G4" t="n">
-        <v>572.76</v>
+        <v>142.64</v>
       </c>
       <c r="H4" t="n">
-        <v>16214.16</v>
+        <v>4098.01</v>
       </c>
       <c r="I4" t="n">
-        <v>25369.89</v>
+        <v>8181.44</v>
       </c>
       <c r="J4" t="n">
-        <v>25369.89</v>
+        <v>8181.44</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -609,37 +609,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>45664</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>21500</v>
+        <v>520</v>
       </c>
       <c r="F5" t="n">
-        <v>77467.64</v>
+        <v>73251.91</v>
       </c>
       <c r="G5" t="n">
-        <v>1140.21</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>51164.68</v>
+        <v>35217.26</v>
       </c>
       <c r="I5" t="n">
-        <v>76327.42999999999</v>
+        <v>73251.91</v>
       </c>
       <c r="J5" t="n">
-        <v>76327.42999999999</v>
+        <v>73251.91</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -648,37 +648,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>2400</v>
+        <v>3800</v>
       </c>
       <c r="F6" t="n">
-        <v>38913.98</v>
+        <v>486638.55</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>12508.64</v>
       </c>
       <c r="H6" t="n">
-        <v>24321.24</v>
+        <v>268931.83</v>
       </c>
       <c r="I6" t="n">
-        <v>38913.98</v>
+        <v>474129.91</v>
       </c>
       <c r="J6" t="n">
-        <v>38913.98</v>
+        <v>474129.91</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -687,37 +687,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>45668</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>2400</v>
+        <v>520</v>
       </c>
       <c r="F7" t="n">
-        <v>51885.3</v>
+        <v>106548.23</v>
       </c>
       <c r="G7" t="n">
-        <v>1909.2</v>
+        <v>2738.73</v>
       </c>
       <c r="H7" t="n">
-        <v>32428.32</v>
+        <v>51225.11</v>
       </c>
       <c r="I7" t="n">
-        <v>49976.1</v>
+        <v>103809.5</v>
       </c>
       <c r="J7" t="n">
-        <v>49976.1</v>
+        <v>103809.5</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -726,12 +726,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -741,22 +741,22 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>8900</v>
+        <v>3800</v>
       </c>
       <c r="F8" t="n">
-        <v>16034</v>
+        <v>48663.85</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>833.91</v>
       </c>
       <c r="H8" t="n">
-        <v>10629.28</v>
+        <v>26893.18</v>
       </c>
       <c r="I8" t="n">
-        <v>16034</v>
+        <v>47829.94</v>
       </c>
       <c r="J8" t="n">
-        <v>16034</v>
+        <v>47829.94</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -765,37 +765,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>21500</v>
+        <v>520</v>
       </c>
       <c r="F9" t="n">
-        <v>77467.64</v>
+        <v>33296.32</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1426.42</v>
       </c>
       <c r="H9" t="n">
-        <v>51164.68</v>
+        <v>16007.85</v>
       </c>
       <c r="I9" t="n">
-        <v>77467.64</v>
+        <v>31869.9</v>
       </c>
       <c r="J9" t="n">
-        <v>77467.64</v>
+        <v>31869.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -804,37 +804,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v>45674</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>1200</v>
+        <v>3800</v>
       </c>
       <c r="F10" t="n">
-        <v>54047.19</v>
+        <v>486638.55</v>
       </c>
       <c r="G10" t="n">
-        <v>795.5</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>36932.25</v>
+        <v>268931.83</v>
       </c>
       <c r="I10" t="n">
-        <v>53251.69</v>
+        <v>486638.55</v>
       </c>
       <c r="J10" t="n">
-        <v>53251.69</v>
+        <v>486638.55</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -843,37 +843,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>2400</v>
+        <v>3800</v>
       </c>
       <c r="F11" t="n">
-        <v>82151.73</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>51344.83</v>
+        <v>53786.37</v>
       </c>
       <c r="I11" t="n">
-        <v>82151.73</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>82151.73</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -882,37 +882,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="D12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>8900</v>
+        <v>950</v>
       </c>
       <c r="F12" t="n">
-        <v>352748.01</v>
+        <v>243319.27</v>
       </c>
       <c r="G12" t="n">
-        <v>7787.93</v>
+        <v>6254.32</v>
       </c>
       <c r="H12" t="n">
-        <v>233844.18</v>
+        <v>117817.75</v>
       </c>
       <c r="I12" t="n">
-        <v>344960.08</v>
+        <v>237064.95</v>
       </c>
       <c r="J12" t="n">
-        <v>344960.08</v>
+        <v>237064.95</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -921,37 +921,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>650</v>
+        <v>3800</v>
       </c>
       <c r="F13" t="n">
-        <v>17565.34</v>
+        <v>778621.6800000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>33356.36</v>
       </c>
       <c r="H13" t="n">
-        <v>11890.38</v>
+        <v>430290.93</v>
       </c>
       <c r="I13" t="n">
-        <v>17565.34</v>
+        <v>745265.3199999999</v>
       </c>
       <c r="J13" t="n">
-        <v>17565.34</v>
+        <v>745265.3199999999</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -975,22 +975,22 @@
         <v>17</v>
       </c>
       <c r="E14" t="n">
-        <v>8900</v>
+        <v>950</v>
       </c>
       <c r="F14" t="n">
-        <v>272578</v>
+        <v>206821.38</v>
       </c>
       <c r="G14" t="n">
-        <v>4011.96</v>
+        <v>8860.280000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>180697.78</v>
+        <v>100145.09</v>
       </c>
       <c r="I14" t="n">
-        <v>268566.04</v>
+        <v>197961.1</v>
       </c>
       <c r="J14" t="n">
-        <v>268566.04</v>
+        <v>197961.1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -999,37 +999,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="F15" t="n">
-        <v>24591.47</v>
+        <v>60829.82</v>
       </c>
       <c r="G15" t="n">
-        <v>361.95</v>
+        <v>1042.39</v>
       </c>
       <c r="H15" t="n">
-        <v>16646.54</v>
+        <v>29454.44</v>
       </c>
       <c r="I15" t="n">
-        <v>24229.52</v>
+        <v>59787.43</v>
       </c>
       <c r="J15" t="n">
-        <v>24229.52</v>
+        <v>59787.43</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1038,37 +1038,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="F16" t="n">
-        <v>7566.61</v>
+        <v>973277.1</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>16678.18</v>
       </c>
       <c r="H16" t="n">
-        <v>5044.4</v>
+        <v>537863.66</v>
       </c>
       <c r="I16" t="n">
-        <v>7566.61</v>
+        <v>956598.92</v>
       </c>
       <c r="J16" t="n">
-        <v>7566.61</v>
+        <v>956598.92</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1077,37 +1077,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>2400</v>
+        <v>1650</v>
       </c>
       <c r="F17" t="n">
-        <v>77827.96000000001</v>
+        <v>295825.01</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>48642.47</v>
+        <v>147016.07</v>
       </c>
       <c r="I17" t="n">
-        <v>77827.96000000001</v>
+        <v>295825.01</v>
       </c>
       <c r="J17" t="n">
-        <v>77827.96000000001</v>
+        <v>295825.01</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1116,37 +1116,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D18" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>15400</v>
+        <v>1650</v>
       </c>
       <c r="F18" t="n">
-        <v>638117.1800000001</v>
+        <v>253564.3</v>
       </c>
       <c r="G18" t="n">
-        <v>14088.27</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>406074.57</v>
+        <v>126013.77</v>
       </c>
       <c r="I18" t="n">
-        <v>624028.91</v>
+        <v>253564.3</v>
       </c>
       <c r="J18" t="n">
-        <v>624028.91</v>
+        <v>253564.3</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1155,37 +1155,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>15400</v>
+        <v>390</v>
       </c>
       <c r="F19" t="n">
-        <v>638117.1800000001</v>
+        <v>79911.17</v>
       </c>
       <c r="G19" t="n">
-        <v>14088.27</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>406074.57</v>
+        <v>36882.08</v>
       </c>
       <c r="I19" t="n">
-        <v>624028.91</v>
+        <v>79911.17</v>
       </c>
       <c r="J19" t="n">
-        <v>624028.91</v>
+        <v>79911.17</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1194,37 +1194,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>4200</v>
+        <v>1950</v>
       </c>
       <c r="F20" t="n">
-        <v>37833.03</v>
+        <v>224750.17</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>25222.02</v>
+        <v>121019.32</v>
       </c>
       <c r="I20" t="n">
-        <v>37833.03</v>
+        <v>224750.17</v>
       </c>
       <c r="J20" t="n">
-        <v>37833.03</v>
+        <v>224750.17</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1233,37 +1233,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="D21" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>8900</v>
+        <v>520</v>
       </c>
       <c r="F21" t="n">
-        <v>368782.01</v>
+        <v>19977.79</v>
       </c>
       <c r="G21" t="n">
-        <v>8141.92</v>
+        <v>342.34</v>
       </c>
       <c r="H21" t="n">
-        <v>244473.46</v>
+        <v>9604.709999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>360640.09</v>
+        <v>19635.45</v>
       </c>
       <c r="J21" t="n">
-        <v>360640.09</v>
+        <v>19635.45</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1272,37 +1272,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="F22" t="n">
-        <v>25762.49</v>
+        <v>48663.85</v>
       </c>
       <c r="G22" t="n">
-        <v>379.19</v>
+        <v>2084.77</v>
       </c>
       <c r="H22" t="n">
-        <v>17439.23</v>
+        <v>23563.55</v>
       </c>
       <c r="I22" t="n">
-        <v>25383.3</v>
+        <v>46579.08</v>
       </c>
       <c r="J22" t="n">
-        <v>25383.3</v>
+        <v>46579.08</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,37 +1311,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F23" t="n">
-        <v>136198.92</v>
+        <v>16648.16</v>
       </c>
       <c r="G23" t="n">
-        <v>5011.64</v>
+        <v>285.28</v>
       </c>
       <c r="H23" t="n">
-        <v>90799.28</v>
+        <v>8196.02</v>
       </c>
       <c r="I23" t="n">
-        <v>131187.28</v>
+        <v>16362.88</v>
       </c>
       <c r="J23" t="n">
-        <v>131187.28</v>
+        <v>16362.88</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,12 +1350,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1365,22 +1365,22 @@
         <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>15400</v>
+        <v>520</v>
       </c>
       <c r="F24" t="n">
-        <v>166465.35</v>
+        <v>39955.59</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1027.02</v>
       </c>
       <c r="H24" t="n">
-        <v>105932.5</v>
+        <v>19209.42</v>
       </c>
       <c r="I24" t="n">
-        <v>166465.35</v>
+        <v>38928.57</v>
       </c>
       <c r="J24" t="n">
-        <v>166465.35</v>
+        <v>38928.57</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,37 +1389,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="F25" t="n">
-        <v>19907.38</v>
+        <v>72995.78</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>13475.77</v>
+        <v>35345.33</v>
       </c>
       <c r="I25" t="n">
-        <v>19907.38</v>
+        <v>72995.78</v>
       </c>
       <c r="J25" t="n">
-        <v>19907.38</v>
+        <v>72995.78</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1428,37 +1428,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E26" t="n">
-        <v>1200</v>
+        <v>950</v>
       </c>
       <c r="F26" t="n">
-        <v>10809.44</v>
+        <v>182489.46</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>7386.45</v>
+        <v>88363.32000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>10809.44</v>
+        <v>182489.46</v>
       </c>
       <c r="J26" t="n">
-        <v>10809.44</v>
+        <v>182489.46</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F27" t="n">
-        <v>38733.82</v>
+        <v>16648.16</v>
       </c>
       <c r="G27" t="n">
-        <v>570.11</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>25582.34</v>
+        <v>8196.02</v>
       </c>
       <c r="I27" t="n">
-        <v>38163.71</v>
+        <v>16648.16</v>
       </c>
       <c r="J27" t="n">
-        <v>38163.71</v>
+        <v>16648.16</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1506,37 +1506,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="D28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>650</v>
+        <v>1950</v>
       </c>
       <c r="F28" t="n">
-        <v>17565.34</v>
+        <v>249722.41</v>
       </c>
       <c r="G28" t="n">
-        <v>646.34</v>
+        <v>10698.18</v>
       </c>
       <c r="H28" t="n">
-        <v>11890.38</v>
+        <v>134465.91</v>
       </c>
       <c r="I28" t="n">
-        <v>16919</v>
+        <v>239024.23</v>
       </c>
       <c r="J28" t="n">
-        <v>16919</v>
+        <v>239024.23</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1545,37 +1545,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
-        <v>4200</v>
+        <v>520</v>
       </c>
       <c r="F29" t="n">
-        <v>22699.82</v>
+        <v>119866.76</v>
       </c>
       <c r="G29" t="n">
-        <v>334.11</v>
+        <v>3081.07</v>
       </c>
       <c r="H29" t="n">
-        <v>15133.21</v>
+        <v>57628.25</v>
       </c>
       <c r="I29" t="n">
-        <v>22365.71</v>
+        <v>116785.69</v>
       </c>
       <c r="J29" t="n">
-        <v>22365.71</v>
+        <v>116785.69</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1584,37 +1584,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>21500</v>
+        <v>3800</v>
       </c>
       <c r="F30" t="n">
-        <v>658474.96</v>
+        <v>340646.98</v>
       </c>
       <c r="G30" t="n">
-        <v>14537.73</v>
+        <v>5837.36</v>
       </c>
       <c r="H30" t="n">
-        <v>434899.74</v>
+        <v>188252.28</v>
       </c>
       <c r="I30" t="n">
-        <v>643937.23</v>
+        <v>334809.62</v>
       </c>
       <c r="J30" t="n">
-        <v>643937.23</v>
+        <v>334809.62</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1623,37 +1623,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>2400</v>
+        <v>520</v>
       </c>
       <c r="F31" t="n">
-        <v>82151.73</v>
+        <v>13318.53</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>228.23</v>
       </c>
       <c r="H31" t="n">
-        <v>51344.83</v>
+        <v>6403.14</v>
       </c>
       <c r="I31" t="n">
-        <v>82151.73</v>
+        <v>13090.3</v>
       </c>
       <c r="J31" t="n">
-        <v>82151.73</v>
+        <v>13090.3</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1662,37 +1662,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="D32" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>650</v>
+        <v>3800</v>
       </c>
       <c r="F32" t="n">
-        <v>24591.47</v>
+        <v>583966.26</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>15010.36</v>
       </c>
       <c r="H32" t="n">
-        <v>16646.54</v>
+        <v>322718.2</v>
       </c>
       <c r="I32" t="n">
-        <v>24591.47</v>
+        <v>568955.9</v>
       </c>
       <c r="J32" t="n">
-        <v>24591.47</v>
+        <v>568955.9</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1701,37 +1701,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D33" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>21500</v>
+        <v>950</v>
       </c>
       <c r="F33" t="n">
-        <v>852144.0600000001</v>
+        <v>182489.46</v>
       </c>
       <c r="G33" t="n">
-        <v>31355.88</v>
+        <v>4690.74</v>
       </c>
       <c r="H33" t="n">
-        <v>562811.4300000001</v>
+        <v>88363.32000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>820788.1800000001</v>
+        <v>177798.72</v>
       </c>
       <c r="J33" t="n">
-        <v>820788.1800000001</v>
+        <v>177798.72</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1740,37 +1740,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="D34" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E34" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F34" t="n">
-        <v>400850.01</v>
+        <v>133185.29</v>
       </c>
       <c r="G34" t="n">
-        <v>14749.86</v>
+        <v>3423.42</v>
       </c>
       <c r="H34" t="n">
-        <v>265732.03</v>
+        <v>65568.14</v>
       </c>
       <c r="I34" t="n">
-        <v>386100.15</v>
+        <v>129761.87</v>
       </c>
       <c r="J34" t="n">
-        <v>386100.15</v>
+        <v>129761.87</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1779,37 +1779,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E35" t="n">
-        <v>8900</v>
+        <v>520</v>
       </c>
       <c r="F35" t="n">
-        <v>400850.01</v>
+        <v>113207.49</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1939.94</v>
       </c>
       <c r="H35" t="n">
-        <v>265732.03</v>
+        <v>54426.68</v>
       </c>
       <c r="I35" t="n">
-        <v>400850.01</v>
+        <v>111267.55</v>
       </c>
       <c r="J35" t="n">
-        <v>400850.01</v>
+        <v>111267.55</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1818,37 +1818,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E36" t="n">
-        <v>1850</v>
+        <v>950</v>
       </c>
       <c r="F36" t="n">
-        <v>13331.64</v>
+        <v>170323.49</v>
       </c>
       <c r="G36" t="n">
-        <v>490.56</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>9007.870000000001</v>
+        <v>82472.42999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>12841.08</v>
+        <v>170323.49</v>
       </c>
       <c r="J36" t="n">
-        <v>12841.08</v>
+        <v>170323.49</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1857,12 +1857,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
@@ -1872,22 +1872,22 @@
         <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>15400</v>
+        <v>1650</v>
       </c>
       <c r="F37" t="n">
-        <v>166465.35</v>
+        <v>126782.15</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>5431.38</v>
       </c>
       <c r="H37" t="n">
-        <v>105932.5</v>
+        <v>63006.89</v>
       </c>
       <c r="I37" t="n">
-        <v>166465.35</v>
+        <v>121350.77</v>
       </c>
       <c r="J37" t="n">
-        <v>166465.35</v>
+        <v>121350.77</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1896,37 +1896,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>1200</v>
+        <v>1950</v>
       </c>
       <c r="F38" t="n">
-        <v>25942.65</v>
+        <v>99888.97</v>
       </c>
       <c r="G38" t="n">
-        <v>954.6</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>17727.48</v>
+        <v>53786.37</v>
       </c>
       <c r="I38" t="n">
-        <v>24988.05</v>
+        <v>99888.97</v>
       </c>
       <c r="J38" t="n">
-        <v>24988.05</v>
+        <v>99888.97</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1935,37 +1935,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>45732</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>15400</v>
+        <v>950</v>
       </c>
       <c r="F39" t="n">
-        <v>83232.67999999999</v>
+        <v>121659.64</v>
       </c>
       <c r="G39" t="n">
-        <v>1225.07</v>
+        <v>2084.77</v>
       </c>
       <c r="H39" t="n">
-        <v>52966.25</v>
+        <v>58908.88</v>
       </c>
       <c r="I39" t="n">
-        <v>82007.61</v>
+        <v>119574.87</v>
       </c>
       <c r="J39" t="n">
-        <v>82007.61</v>
+        <v>119574.87</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1974,37 +1974,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>15400</v>
+        <v>1650</v>
       </c>
       <c r="F40" t="n">
-        <v>138721.13</v>
+        <v>295825.01</v>
       </c>
       <c r="G40" t="n">
-        <v>2041.78</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>88277.08</v>
+        <v>147016.07</v>
       </c>
       <c r="I40" t="n">
-        <v>136679.35</v>
+        <v>295825.01</v>
       </c>
       <c r="J40" t="n">
-        <v>136679.35</v>
+        <v>295825.01</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2013,37 +2013,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D41" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E41" t="n">
-        <v>4200</v>
+        <v>1950</v>
       </c>
       <c r="F41" t="n">
-        <v>128632.32</v>
+        <v>374583.62</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>85754.88</v>
+        <v>201698.87</v>
       </c>
       <c r="I41" t="n">
-        <v>128632.32</v>
+        <v>374583.62</v>
       </c>
       <c r="J41" t="n">
-        <v>128632.32</v>
+        <v>374583.62</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2052,37 +2052,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>45738</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E42" t="n">
-        <v>8900</v>
+        <v>1650</v>
       </c>
       <c r="F42" t="n">
-        <v>96204</v>
+        <v>295825.01</v>
       </c>
       <c r="G42" t="n">
-        <v>3539.97</v>
+        <v>5069.29</v>
       </c>
       <c r="H42" t="n">
-        <v>63775.69</v>
+        <v>147016.07</v>
       </c>
       <c r="I42" t="n">
-        <v>92664.03</v>
+        <v>290755.72</v>
       </c>
       <c r="J42" t="n">
-        <v>92664.03</v>
+        <v>290755.72</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2091,37 +2091,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D43" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E43" t="n">
-        <v>650</v>
+        <v>3800</v>
       </c>
       <c r="F43" t="n">
-        <v>22249.43</v>
+        <v>632630.11</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>10840.82</v>
       </c>
       <c r="H43" t="n">
-        <v>15061.15</v>
+        <v>349611.38</v>
       </c>
       <c r="I43" t="n">
-        <v>22249.43</v>
+        <v>621789.29</v>
       </c>
       <c r="J43" t="n">
-        <v>22249.43</v>
+        <v>621789.29</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2130,37 +2130,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>1850</v>
+        <v>3800</v>
       </c>
       <c r="F44" t="n">
-        <v>9998.73</v>
+        <v>243319.27</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>10423.86</v>
       </c>
       <c r="H44" t="n">
-        <v>6755.9</v>
+        <v>134465.91</v>
       </c>
       <c r="I44" t="n">
-        <v>9998.73</v>
+        <v>232895.41</v>
       </c>
       <c r="J44" t="n">
-        <v>9998.73</v>
+        <v>232895.41</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2169,37 +2169,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="D45" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>15400</v>
+        <v>3800</v>
       </c>
       <c r="F45" t="n">
-        <v>582628.73</v>
+        <v>243319.27</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>370763.74</v>
+        <v>134465.91</v>
       </c>
       <c r="I45" t="n">
-        <v>582628.73</v>
+        <v>243319.27</v>
       </c>
       <c r="J45" t="n">
-        <v>582628.73</v>
+        <v>243319.27</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2208,37 +2208,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E46" t="n">
-        <v>2400</v>
+        <v>520</v>
       </c>
       <c r="F46" t="n">
-        <v>86475.50999999999</v>
+        <v>79911.17</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1369.37</v>
       </c>
       <c r="H46" t="n">
-        <v>54047.19</v>
+        <v>38418.83</v>
       </c>
       <c r="I46" t="n">
-        <v>86475.50999999999</v>
+        <v>78541.8</v>
       </c>
       <c r="J46" t="n">
-        <v>86475.50999999999</v>
+        <v>78541.8</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2247,37 +2247,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D47" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>15400</v>
+        <v>1650</v>
       </c>
       <c r="F47" t="n">
-        <v>582628.73</v>
+        <v>42260.72</v>
       </c>
       <c r="G47" t="n">
-        <v>8575.469999999999</v>
+        <v>1810.46</v>
       </c>
       <c r="H47" t="n">
-        <v>370763.74</v>
+        <v>21002.3</v>
       </c>
       <c r="I47" t="n">
-        <v>574053.26</v>
+        <v>40450.26</v>
       </c>
       <c r="J47" t="n">
-        <v>574053.26</v>
+        <v>40450.26</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2286,37 +2286,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="D48" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E48" t="n">
-        <v>1200</v>
+        <v>950</v>
       </c>
       <c r="F48" t="n">
-        <v>47561.53</v>
+        <v>182489.46</v>
       </c>
       <c r="G48" t="n">
-        <v>1050.06</v>
+        <v>3127.16</v>
       </c>
       <c r="H48" t="n">
-        <v>32500.38</v>
+        <v>88363.32000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>46511.47</v>
+        <v>179362.3</v>
       </c>
       <c r="J48" t="n">
-        <v>46511.47</v>
+        <v>179362.3</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2325,12 +2325,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
@@ -2340,22 +2340,22 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>21500</v>
+        <v>390</v>
       </c>
       <c r="F49" t="n">
-        <v>116201.46</v>
+        <v>14983.34</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>641.89</v>
       </c>
       <c r="H49" t="n">
-        <v>76747.00999999999</v>
+        <v>6915.39</v>
       </c>
       <c r="I49" t="n">
-        <v>116201.46</v>
+        <v>14341.45</v>
       </c>
       <c r="J49" t="n">
-        <v>116201.46</v>
+        <v>14341.45</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2364,37 +2364,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E50" t="n">
-        <v>21500</v>
+        <v>1650</v>
       </c>
       <c r="F50" t="n">
-        <v>542273.49</v>
+        <v>253564.3</v>
       </c>
       <c r="G50" t="n">
-        <v>11972.24</v>
+        <v>6517.66</v>
       </c>
       <c r="H50" t="n">
-        <v>358152.73</v>
+        <v>126013.77</v>
       </c>
       <c r="I50" t="n">
-        <v>530301.25</v>
+        <v>247046.64</v>
       </c>
       <c r="J50" t="n">
-        <v>530301.25</v>
+        <v>247046.64</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2403,37 +2403,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="D51" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>1200</v>
+        <v>950</v>
       </c>
       <c r="F51" t="n">
-        <v>23780.76</v>
+        <v>109493.67</v>
       </c>
       <c r="G51" t="n">
-        <v>875.05</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>16250.19</v>
+        <v>53017.99</v>
       </c>
       <c r="I51" t="n">
-        <v>22905.71</v>
+        <v>109493.67</v>
       </c>
       <c r="J51" t="n">
-        <v>22905.71</v>
+        <v>109493.67</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2442,37 +2442,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>45759</v>
       </c>
       <c r="D52" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E52" t="n">
-        <v>650</v>
+        <v>3800</v>
       </c>
       <c r="F52" t="n">
-        <v>26933.52</v>
+        <v>291983.13</v>
       </c>
       <c r="G52" t="n">
-        <v>396.42</v>
+        <v>7505.18</v>
       </c>
       <c r="H52" t="n">
-        <v>18231.92</v>
+        <v>161359.1</v>
       </c>
       <c r="I52" t="n">
-        <v>26537.1</v>
+        <v>284477.95</v>
       </c>
       <c r="J52" t="n">
-        <v>26537.1</v>
+        <v>284477.95</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2481,37 +2481,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="D53" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>650</v>
+        <v>1650</v>
       </c>
       <c r="F53" t="n">
-        <v>15223.29</v>
+        <v>84521.42999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1448.37</v>
       </c>
       <c r="H53" t="n">
-        <v>10305</v>
+        <v>42004.59</v>
       </c>
       <c r="I53" t="n">
-        <v>15223.29</v>
+        <v>83073.06</v>
       </c>
       <c r="J53" t="n">
-        <v>15223.29</v>
+        <v>83073.06</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2520,37 +2520,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D54" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E54" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="F54" t="n">
-        <v>19907.38</v>
+        <v>182489.46</v>
       </c>
       <c r="G54" t="n">
-        <v>732.52</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>13475.77</v>
+        <v>88363.32000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>19174.86</v>
+        <v>182489.46</v>
       </c>
       <c r="J54" t="n">
-        <v>19174.86</v>
+        <v>182489.46</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2559,37 +2559,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E55" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="F55" t="n">
-        <v>9368.18</v>
+        <v>194655.42</v>
       </c>
       <c r="G55" t="n">
-        <v>206.83</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>6341.54</v>
+        <v>94254.2</v>
       </c>
       <c r="I55" t="n">
-        <v>9161.35</v>
+        <v>194655.42</v>
       </c>
       <c r="J55" t="n">
-        <v>9161.35</v>
+        <v>194655.42</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2598,37 +2598,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v>45767</v>
       </c>
       <c r="D56" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F56" t="n">
-        <v>416163.38</v>
+        <v>24972.24</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>641.89</v>
       </c>
       <c r="H56" t="n">
-        <v>264831.24</v>
+        <v>12294.03</v>
       </c>
       <c r="I56" t="n">
-        <v>416163.38</v>
+        <v>24330.35</v>
       </c>
       <c r="J56" t="n">
-        <v>416163.38</v>
+        <v>24330.35</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2637,37 +2637,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E57" t="n">
-        <v>4200</v>
+        <v>950</v>
       </c>
       <c r="F57" t="n">
-        <v>15133.21</v>
+        <v>182489.46</v>
       </c>
       <c r="G57" t="n">
-        <v>222.74</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>10088.81</v>
+        <v>88363.32000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>14910.47</v>
+        <v>182489.46</v>
       </c>
       <c r="J57" t="n">
-        <v>14910.47</v>
+        <v>182489.46</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2676,37 +2676,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E58" t="n">
-        <v>2400</v>
+        <v>950</v>
       </c>
       <c r="F58" t="n">
-        <v>34590.2</v>
+        <v>145991.56</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>21618.88</v>
+        <v>70690.64999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>34590.2</v>
+        <v>145991.56</v>
       </c>
       <c r="J58" t="n">
-        <v>34590.2</v>
+        <v>145991.56</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2715,37 +2715,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="D59" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
-        <v>650</v>
+        <v>1950</v>
       </c>
       <c r="F59" t="n">
-        <v>22249.43</v>
+        <v>149833.45</v>
       </c>
       <c r="G59" t="n">
-        <v>327.48</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>15061.15</v>
+        <v>80679.55</v>
       </c>
       <c r="I59" t="n">
-        <v>21921.95</v>
+        <v>149833.45</v>
       </c>
       <c r="J59" t="n">
-        <v>21921.95</v>
+        <v>149833.45</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2754,37 +2754,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="D60" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E60" t="n">
-        <v>8900</v>
+        <v>1650</v>
       </c>
       <c r="F60" t="n">
-        <v>256544</v>
+        <v>169042.86</v>
       </c>
       <c r="G60" t="n">
-        <v>9439.91</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>170068.5</v>
+        <v>84009.17999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>247104.09</v>
+        <v>169042.86</v>
       </c>
       <c r="J60" t="n">
-        <v>247104.09</v>
+        <v>169042.86</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2793,37 +2793,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>21500</v>
+        <v>520</v>
       </c>
       <c r="F61" t="n">
-        <v>387338.21</v>
+        <v>33296.32</v>
       </c>
       <c r="G61" t="n">
-        <v>8551.6</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>255823.38</v>
+        <v>16007.85</v>
       </c>
       <c r="I61" t="n">
-        <v>378786.61</v>
+        <v>33296.32</v>
       </c>
       <c r="J61" t="n">
-        <v>378786.61</v>
+        <v>33296.32</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2832,37 +2832,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D62" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E62" t="n">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="F62" t="n">
-        <v>98365.89</v>
+        <v>583966.26</v>
       </c>
       <c r="G62" t="n">
-        <v>3619.52</v>
+        <v>25017.27</v>
       </c>
       <c r="H62" t="n">
-        <v>65577.25999999999</v>
+        <v>322718.2</v>
       </c>
       <c r="I62" t="n">
-        <v>94746.37</v>
+        <v>558948.99</v>
       </c>
       <c r="J62" t="n">
-        <v>94746.37</v>
+        <v>558948.99</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2871,37 +2871,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v>45781</v>
       </c>
       <c r="D63" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E63" t="n">
-        <v>1200</v>
+        <v>390</v>
       </c>
       <c r="F63" t="n">
-        <v>15133.21</v>
+        <v>89900.07000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>556.85</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>10341.03</v>
+        <v>41492.34</v>
       </c>
       <c r="I63" t="n">
-        <v>14576.36</v>
+        <v>89900.07000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>14576.36</v>
+        <v>89900.07000000001</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2910,37 +2910,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E64" t="n">
-        <v>1850</v>
+        <v>3800</v>
       </c>
       <c r="F64" t="n">
-        <v>6665.82</v>
+        <v>486638.55</v>
       </c>
       <c r="G64" t="n">
-        <v>98.11</v>
+        <v>12508.64</v>
       </c>
       <c r="H64" t="n">
-        <v>4503.93</v>
+        <v>268931.83</v>
       </c>
       <c r="I64" t="n">
-        <v>6567.71</v>
+        <v>474129.91</v>
       </c>
       <c r="J64" t="n">
-        <v>6567.71</v>
+        <v>474129.91</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2949,37 +2949,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D65" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E65" t="n">
-        <v>21500</v>
+        <v>1650</v>
       </c>
       <c r="F65" t="n">
-        <v>387338.21</v>
+        <v>295825.01</v>
       </c>
       <c r="G65" t="n">
-        <v>14252.67</v>
+        <v>7603.93</v>
       </c>
       <c r="H65" t="n">
-        <v>255823.38</v>
+        <v>147016.07</v>
       </c>
       <c r="I65" t="n">
-        <v>373085.54</v>
+        <v>288221.08</v>
       </c>
       <c r="J65" t="n">
-        <v>373085.54</v>
+        <v>288221.08</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2988,37 +2988,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>45787</v>
       </c>
       <c r="D66" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E66" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F66" t="n">
-        <v>105932.5</v>
+        <v>91564.88</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>70621.66</v>
+        <v>45078.1</v>
       </c>
       <c r="I66" t="n">
-        <v>105932.5</v>
+        <v>91564.88</v>
       </c>
       <c r="J66" t="n">
-        <v>105932.5</v>
+        <v>91564.88</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3027,37 +3027,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D67" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E67" t="n">
-        <v>15400</v>
+        <v>390</v>
       </c>
       <c r="F67" t="n">
-        <v>665861.4</v>
+        <v>84905.62</v>
       </c>
       <c r="G67" t="n">
-        <v>9800.540000000001</v>
+        <v>1454.95</v>
       </c>
       <c r="H67" t="n">
-        <v>423729.98</v>
+        <v>39187.21</v>
       </c>
       <c r="I67" t="n">
-        <v>656060.86</v>
+        <v>83450.67</v>
       </c>
       <c r="J67" t="n">
-        <v>656060.86</v>
+        <v>83450.67</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3066,37 +3066,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="D68" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E68" t="n">
-        <v>2400</v>
+        <v>520</v>
       </c>
       <c r="F68" t="n">
-        <v>51885.3</v>
+        <v>119866.76</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>5135.12</v>
       </c>
       <c r="H68" t="n">
-        <v>32428.32</v>
+        <v>57628.25</v>
       </c>
       <c r="I68" t="n">
-        <v>51885.3</v>
+        <v>114731.64</v>
       </c>
       <c r="J68" t="n">
-        <v>51885.3</v>
+        <v>114731.64</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3105,37 +3105,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>1850</v>
+        <v>520</v>
       </c>
       <c r="F69" t="n">
-        <v>63325.29</v>
+        <v>33296.32</v>
       </c>
       <c r="G69" t="n">
-        <v>2330.15</v>
+        <v>855.85</v>
       </c>
       <c r="H69" t="n">
-        <v>42787.36</v>
+        <v>16007.85</v>
       </c>
       <c r="I69" t="n">
-        <v>60995.14</v>
+        <v>32440.47</v>
       </c>
       <c r="J69" t="n">
-        <v>60995.14</v>
+        <v>32440.47</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3144,37 +3144,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v>45795</v>
       </c>
       <c r="D70" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E70" t="n">
-        <v>650</v>
+        <v>520</v>
       </c>
       <c r="F70" t="n">
-        <v>21078.4</v>
+        <v>26637.06</v>
       </c>
       <c r="G70" t="n">
-        <v>310.24</v>
+        <v>1141.14</v>
       </c>
       <c r="H70" t="n">
-        <v>14268.46</v>
+        <v>12806.28</v>
       </c>
       <c r="I70" t="n">
-        <v>20768.16</v>
+        <v>25495.92</v>
       </c>
       <c r="J70" t="n">
-        <v>20768.16</v>
+        <v>25495.92</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3183,37 +3183,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D71" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>2400</v>
+        <v>1950</v>
       </c>
       <c r="F71" t="n">
-        <v>73504.17999999999</v>
+        <v>149833.45</v>
       </c>
       <c r="G71" t="n">
-        <v>1622.82</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>45940.11</v>
+        <v>80679.55</v>
       </c>
       <c r="I71" t="n">
-        <v>71881.36</v>
+        <v>149833.45</v>
       </c>
       <c r="J71" t="n">
-        <v>71881.36</v>
+        <v>149833.45</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3222,37 +3222,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E72" t="n">
-        <v>15400</v>
+        <v>950</v>
       </c>
       <c r="F72" t="n">
-        <v>554884.5</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>20417.78</v>
+        <v>1667.82</v>
       </c>
       <c r="H72" t="n">
-        <v>353108.32</v>
+        <v>47127.1</v>
       </c>
       <c r="I72" t="n">
-        <v>534466.72</v>
+        <v>95659.89</v>
       </c>
       <c r="J72" t="n">
-        <v>534466.72</v>
+        <v>95659.89</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3261,37 +3261,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v>45801</v>
       </c>
       <c r="D73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>8900</v>
+        <v>520</v>
       </c>
       <c r="F73" t="n">
-        <v>64136</v>
+        <v>19977.79</v>
       </c>
       <c r="G73" t="n">
-        <v>1415.99</v>
+        <v>342.34</v>
       </c>
       <c r="H73" t="n">
-        <v>42517.12</v>
+        <v>9604.709999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>62720.01</v>
+        <v>19635.45</v>
       </c>
       <c r="J73" t="n">
-        <v>62720.01</v>
+        <v>19635.45</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3300,12 +3300,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -3315,22 +3315,22 @@
         <v>18</v>
       </c>
       <c r="E74" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="F74" t="n">
-        <v>21078.4</v>
+        <v>218987.35</v>
       </c>
       <c r="G74" t="n">
-        <v>310.24</v>
+        <v>3752.59</v>
       </c>
       <c r="H74" t="n">
-        <v>14268.46</v>
+        <v>106035.98</v>
       </c>
       <c r="I74" t="n">
-        <v>20768.16</v>
+        <v>215234.76</v>
       </c>
       <c r="J74" t="n">
-        <v>20768.16</v>
+        <v>215234.76</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3339,37 +3339,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E75" t="n">
-        <v>8900</v>
+        <v>950</v>
       </c>
       <c r="F75" t="n">
-        <v>112238</v>
+        <v>121659.64</v>
       </c>
       <c r="G75" t="n">
-        <v>4129.96</v>
+        <v>5211.93</v>
       </c>
       <c r="H75" t="n">
-        <v>74404.97</v>
+        <v>58908.88</v>
       </c>
       <c r="I75" t="n">
-        <v>108108.04</v>
+        <v>116447.71</v>
       </c>
       <c r="J75" t="n">
-        <v>108108.04</v>
+        <v>116447.71</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3378,37 +3378,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D76" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E76" t="n">
-        <v>2400</v>
+        <v>1650</v>
       </c>
       <c r="F76" t="n">
-        <v>73504.17999999999</v>
+        <v>126782.15</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>5431.38</v>
       </c>
       <c r="H76" t="n">
-        <v>45940.11</v>
+        <v>63006.89</v>
       </c>
       <c r="I76" t="n">
-        <v>73504.17999999999</v>
+        <v>121350.77</v>
       </c>
       <c r="J76" t="n">
-        <v>73504.17999999999</v>
+        <v>121350.77</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3417,37 +3417,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E77" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F77" t="n">
-        <v>16664.55</v>
+        <v>166481.61</v>
       </c>
       <c r="G77" t="n">
-        <v>245.28</v>
+        <v>7132.12</v>
       </c>
       <c r="H77" t="n">
-        <v>11259.83</v>
+        <v>81960.17999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>16419.27</v>
+        <v>159349.49</v>
       </c>
       <c r="J77" t="n">
-        <v>16419.27</v>
+        <v>159349.49</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3456,37 +3456,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="D78" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E78" t="n">
-        <v>21500</v>
+        <v>520</v>
       </c>
       <c r="F78" t="n">
-        <v>658474.96</v>
+        <v>126526.02</v>
       </c>
       <c r="G78" t="n">
-        <v>14537.73</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>434899.74</v>
+        <v>60829.82</v>
       </c>
       <c r="I78" t="n">
-        <v>643937.23</v>
+        <v>126526.02</v>
       </c>
       <c r="J78" t="n">
-        <v>643937.23</v>
+        <v>126526.02</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3495,37 +3495,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D79" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>8900</v>
+        <v>3800</v>
       </c>
       <c r="F79" t="n">
-        <v>176374</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>6489.94</v>
+        <v>4169.55</v>
       </c>
       <c r="H79" t="n">
-        <v>116922.09</v>
+        <v>53786.37</v>
       </c>
       <c r="I79" t="n">
-        <v>169884.06</v>
+        <v>93158.16</v>
       </c>
       <c r="J79" t="n">
-        <v>169884.06</v>
+        <v>93158.16</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3534,37 +3534,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="D80" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E80" t="n">
-        <v>8900</v>
+        <v>950</v>
       </c>
       <c r="F80" t="n">
-        <v>208442</v>
+        <v>85161.75</v>
       </c>
       <c r="G80" t="n">
-        <v>7669.93</v>
+        <v>3648.35</v>
       </c>
       <c r="H80" t="n">
-        <v>138180.65</v>
+        <v>41236.21</v>
       </c>
       <c r="I80" t="n">
-        <v>200772.07</v>
+        <v>81513.39999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>200772.07</v>
+        <v>81513.39999999999</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3573,37 +3573,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="D81" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>15400</v>
+        <v>1650</v>
       </c>
       <c r="F81" t="n">
-        <v>527140.28</v>
+        <v>21130.36</v>
       </c>
       <c r="G81" t="n">
-        <v>7758.76</v>
+        <v>543.14</v>
       </c>
       <c r="H81" t="n">
-        <v>335452.9</v>
+        <v>10501.15</v>
       </c>
       <c r="I81" t="n">
-        <v>519381.52</v>
+        <v>20587.22</v>
       </c>
       <c r="J81" t="n">
-        <v>519381.52</v>
+        <v>20587.22</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3612,37 +3612,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="D82" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E82" t="n">
-        <v>21500</v>
+        <v>950</v>
       </c>
       <c r="F82" t="n">
-        <v>890877.88</v>
+        <v>121659.64</v>
       </c>
       <c r="G82" t="n">
-        <v>32781.15</v>
+        <v>3127.16</v>
       </c>
       <c r="H82" t="n">
-        <v>588393.76</v>
+        <v>58908.88</v>
       </c>
       <c r="I82" t="n">
-        <v>858096.73</v>
+        <v>118532.48</v>
       </c>
       <c r="J82" t="n">
-        <v>858096.73</v>
+        <v>118532.48</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3651,37 +3651,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E83" t="n">
-        <v>21500</v>
+        <v>520</v>
       </c>
       <c r="F83" t="n">
-        <v>38733.82</v>
+        <v>86570.44</v>
       </c>
       <c r="G83" t="n">
-        <v>570.11</v>
+        <v>1483.48</v>
       </c>
       <c r="H83" t="n">
-        <v>25582.34</v>
+        <v>41620.4</v>
       </c>
       <c r="I83" t="n">
-        <v>38163.71</v>
+        <v>85086.96000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>38163.71</v>
+        <v>85086.96000000001</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3690,37 +3690,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="D84" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="F84" t="n">
-        <v>105932.5</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>3897.94</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>70621.66</v>
+        <v>53786.37</v>
       </c>
       <c r="I84" t="n">
-        <v>102034.56</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="J84" t="n">
-        <v>102034.56</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3729,37 +3729,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="D85" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E85" t="n">
-        <v>1850</v>
+        <v>390</v>
       </c>
       <c r="F85" t="n">
-        <v>66658.2</v>
+        <v>79911.17</v>
       </c>
       <c r="G85" t="n">
-        <v>1471.67</v>
+        <v>2054.05</v>
       </c>
       <c r="H85" t="n">
-        <v>45039.33</v>
+        <v>36882.08</v>
       </c>
       <c r="I85" t="n">
-        <v>65186.53</v>
+        <v>77857.12</v>
       </c>
       <c r="J85" t="n">
-        <v>65186.53</v>
+        <v>77857.12</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3768,37 +3768,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="D86" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E86" t="n">
-        <v>1200</v>
+        <v>1950</v>
       </c>
       <c r="F86" t="n">
-        <v>51885.3</v>
+        <v>499444.83</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>35454.96</v>
+        <v>268931.83</v>
       </c>
       <c r="I86" t="n">
-        <v>51885.3</v>
+        <v>499444.83</v>
       </c>
       <c r="J86" t="n">
-        <v>51885.3</v>
+        <v>499444.83</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3807,37 +3807,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="D87" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E87" t="n">
-        <v>21500</v>
+        <v>520</v>
       </c>
       <c r="F87" t="n">
-        <v>232402.93</v>
+        <v>73251.91</v>
       </c>
       <c r="G87" t="n">
-        <v>8551.6</v>
+        <v>1255.25</v>
       </c>
       <c r="H87" t="n">
-        <v>153494.03</v>
+        <v>35217.26</v>
       </c>
       <c r="I87" t="n">
-        <v>223851.33</v>
+        <v>71996.66</v>
       </c>
       <c r="J87" t="n">
-        <v>223851.33</v>
+        <v>71996.66</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3846,37 +3846,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E88" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F88" t="n">
-        <v>21618.88</v>
+        <v>99888.97</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>4279.27</v>
       </c>
       <c r="H88" t="n">
-        <v>13511.8</v>
+        <v>49176.11</v>
       </c>
       <c r="I88" t="n">
-        <v>21618.88</v>
+        <v>95609.7</v>
       </c>
       <c r="J88" t="n">
-        <v>21618.88</v>
+        <v>95609.7</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3885,37 +3885,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="D89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E89" t="n">
-        <v>4200</v>
+        <v>1950</v>
       </c>
       <c r="F89" t="n">
-        <v>52966.25</v>
+        <v>199777.93</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>5135.12</v>
       </c>
       <c r="H89" t="n">
-        <v>35310.83</v>
+        <v>107572.73</v>
       </c>
       <c r="I89" t="n">
-        <v>52966.25</v>
+        <v>194642.81</v>
       </c>
       <c r="J89" t="n">
-        <v>52966.25</v>
+        <v>194642.81</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3924,37 +3924,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="D90" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E90" t="n">
-        <v>650</v>
+        <v>1950</v>
       </c>
       <c r="F90" t="n">
-        <v>16394.31</v>
+        <v>374583.62</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>11097.69</v>
+        <v>201698.87</v>
       </c>
       <c r="I90" t="n">
-        <v>16394.31</v>
+        <v>374583.62</v>
       </c>
       <c r="J90" t="n">
-        <v>16394.31</v>
+        <v>374583.62</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="D91" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
-        <v>1200</v>
+        <v>3800</v>
       </c>
       <c r="F91" t="n">
-        <v>30266.43</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="G91" t="n">
-        <v>1113.7</v>
+        <v>1667.82</v>
       </c>
       <c r="H91" t="n">
-        <v>20682.06</v>
+        <v>53786.37</v>
       </c>
       <c r="I91" t="n">
-        <v>29152.73</v>
+        <v>95659.89</v>
       </c>
       <c r="J91" t="n">
-        <v>29152.73</v>
+        <v>95659.89</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4002,37 +4002,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="D92" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E92" t="n">
-        <v>21500</v>
+        <v>520</v>
       </c>
       <c r="F92" t="n">
-        <v>929611.7</v>
+        <v>133185.29</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>3423.42</v>
       </c>
       <c r="H92" t="n">
-        <v>613976.1</v>
+        <v>64031.39</v>
       </c>
       <c r="I92" t="n">
-        <v>929611.7</v>
+        <v>129761.87</v>
       </c>
       <c r="J92" t="n">
-        <v>929611.7</v>
+        <v>129761.87</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4041,37 +4041,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="D93" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E93" t="n">
-        <v>8900</v>
+        <v>520</v>
       </c>
       <c r="F93" t="n">
-        <v>272578</v>
+        <v>39955.59</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>684.6799999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>180697.78</v>
+        <v>19209.42</v>
       </c>
       <c r="I93" t="n">
-        <v>272578</v>
+        <v>39270.91</v>
       </c>
       <c r="J93" t="n">
-        <v>272578</v>
+        <v>39270.91</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4080,37 +4080,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="D94" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E94" t="n">
         <v>650</v>
       </c>
       <c r="F94" t="n">
-        <v>25762.49</v>
+        <v>49944.48</v>
       </c>
       <c r="G94" t="n">
-        <v>568.78</v>
+        <v>1283.78</v>
       </c>
       <c r="H94" t="n">
-        <v>17439.23</v>
+        <v>24588.05</v>
       </c>
       <c r="I94" t="n">
-        <v>25193.71</v>
+        <v>48660.7</v>
       </c>
       <c r="J94" t="n">
-        <v>25193.71</v>
+        <v>48660.7</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4119,37 +4119,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="D95" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E95" t="n">
-        <v>2400</v>
+        <v>390</v>
       </c>
       <c r="F95" t="n">
-        <v>47561.53</v>
+        <v>49944.48</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1283.78</v>
       </c>
       <c r="H95" t="n">
-        <v>29725.96</v>
+        <v>23051.3</v>
       </c>
       <c r="I95" t="n">
-        <v>47561.53</v>
+        <v>48660.7</v>
       </c>
       <c r="J95" t="n">
-        <v>47561.53</v>
+        <v>48660.7</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4158,37 +4158,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="D96" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E96" t="n">
-        <v>650</v>
+        <v>3800</v>
       </c>
       <c r="F96" t="n">
-        <v>21078.4</v>
+        <v>632630.11</v>
       </c>
       <c r="G96" t="n">
-        <v>310.24</v>
+        <v>27102.05</v>
       </c>
       <c r="H96" t="n">
-        <v>14268.46</v>
+        <v>349611.38</v>
       </c>
       <c r="I96" t="n">
-        <v>20768.16</v>
+        <v>605528.0600000001</v>
       </c>
       <c r="J96" t="n">
-        <v>20768.16</v>
+        <v>605528.0600000001</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4197,37 +4197,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="D97" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F97" t="n">
-        <v>554884.5</v>
+        <v>58268.56</v>
       </c>
       <c r="G97" t="n">
-        <v>12250.67</v>
+        <v>2496.24</v>
       </c>
       <c r="H97" t="n">
-        <v>353108.32</v>
+        <v>28686.06</v>
       </c>
       <c r="I97" t="n">
-        <v>542633.83</v>
+        <v>55772.32</v>
       </c>
       <c r="J97" t="n">
-        <v>542633.83</v>
+        <v>55772.32</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4236,37 +4236,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="D98" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>1200</v>
+        <v>3800</v>
       </c>
       <c r="F98" t="n">
-        <v>19456.99</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="G98" t="n">
-        <v>715.95</v>
+        <v>1667.82</v>
       </c>
       <c r="H98" t="n">
-        <v>13295.61</v>
+        <v>53786.37</v>
       </c>
       <c r="I98" t="n">
-        <v>18741.04</v>
+        <v>95659.89</v>
       </c>
       <c r="J98" t="n">
-        <v>18741.04</v>
+        <v>95659.89</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4275,37 +4275,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="D99" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E99" t="n">
-        <v>1200</v>
+        <v>1650</v>
       </c>
       <c r="F99" t="n">
-        <v>21618.88</v>
+        <v>338085.73</v>
       </c>
       <c r="G99" t="n">
-        <v>318.2</v>
+        <v>5793.47</v>
       </c>
       <c r="H99" t="n">
-        <v>14772.9</v>
+        <v>168018.36</v>
       </c>
       <c r="I99" t="n">
-        <v>21300.68</v>
+        <v>332292.26</v>
       </c>
       <c r="J99" t="n">
-        <v>21300.68</v>
+        <v>332292.26</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4314,37 +4314,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D100" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
-        <v>1200</v>
+        <v>520</v>
       </c>
       <c r="F100" t="n">
-        <v>49723.42</v>
+        <v>26637.06</v>
       </c>
       <c r="G100" t="n">
-        <v>1097.79</v>
+        <v>684.6799999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>33977.67</v>
+        <v>12806.28</v>
       </c>
       <c r="I100" t="n">
-        <v>48625.63</v>
+        <v>25952.38</v>
       </c>
       <c r="J100" t="n">
-        <v>48625.63</v>
+        <v>25952.38</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4353,12 +4353,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -4368,22 +4368,22 @@
         <v>12</v>
       </c>
       <c r="E101" t="n">
-        <v>21500</v>
+        <v>1950</v>
       </c>
       <c r="F101" t="n">
-        <v>464805.85</v>
+        <v>299666.9</v>
       </c>
       <c r="G101" t="n">
-        <v>17103.21</v>
+        <v>7702.69</v>
       </c>
       <c r="H101" t="n">
-        <v>306988.05</v>
+        <v>161359.1</v>
       </c>
       <c r="I101" t="n">
-        <v>447702.64</v>
+        <v>291964.21</v>
       </c>
       <c r="J101" t="n">
-        <v>447702.64</v>
+        <v>291964.21</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4392,37 +4392,37 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D102" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E102" t="n">
-        <v>15400</v>
+        <v>3800</v>
       </c>
       <c r="F102" t="n">
-        <v>277442.25</v>
+        <v>632630.11</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>176554.16</v>
+        <v>349611.38</v>
       </c>
       <c r="I102" t="n">
-        <v>277442.25</v>
+        <v>632630.11</v>
       </c>
       <c r="J102" t="n">
-        <v>277442.25</v>
+        <v>632630.11</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4431,37 +4431,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D103" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E103" t="n">
-        <v>2400</v>
+        <v>1950</v>
       </c>
       <c r="F103" t="n">
-        <v>56209.08</v>
+        <v>449500.34</v>
       </c>
       <c r="G103" t="n">
-        <v>827.3200000000001</v>
+        <v>7702.69</v>
       </c>
       <c r="H103" t="n">
-        <v>35130.67</v>
+        <v>242038.65</v>
       </c>
       <c r="I103" t="n">
-        <v>55381.76</v>
+        <v>441797.65</v>
       </c>
       <c r="J103" t="n">
-        <v>55381.76</v>
+        <v>441797.65</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4470,37 +4470,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="D104" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E104" t="n">
-        <v>8900</v>
+        <v>390</v>
       </c>
       <c r="F104" t="n">
-        <v>160340</v>
+        <v>84905.62</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>2182.43</v>
       </c>
       <c r="H104" t="n">
-        <v>106292.81</v>
+        <v>39187.21</v>
       </c>
       <c r="I104" t="n">
-        <v>160340</v>
+        <v>82723.19</v>
       </c>
       <c r="J104" t="n">
-        <v>160340</v>
+        <v>82723.19</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4509,37 +4509,37 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D105" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E105" t="n">
-        <v>4200</v>
+        <v>520</v>
       </c>
       <c r="F105" t="n">
-        <v>90799.28</v>
+        <v>133185.29</v>
       </c>
       <c r="G105" t="n">
-        <v>2004.65</v>
+        <v>5705.69</v>
       </c>
       <c r="H105" t="n">
-        <v>60532.85</v>
+        <v>64031.39</v>
       </c>
       <c r="I105" t="n">
-        <v>88794.63</v>
+        <v>127479.6</v>
       </c>
       <c r="J105" t="n">
-        <v>88794.63</v>
+        <v>127479.6</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4548,37 +4548,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D106" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E106" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F106" t="n">
-        <v>665861.4</v>
+        <v>33296.32</v>
       </c>
       <c r="G106" t="n">
-        <v>14700.8</v>
+        <v>855.85</v>
       </c>
       <c r="H106" t="n">
-        <v>423729.98</v>
+        <v>16392.04</v>
       </c>
       <c r="I106" t="n">
-        <v>651160.6</v>
+        <v>32440.47</v>
       </c>
       <c r="J106" t="n">
-        <v>651160.6</v>
+        <v>32440.47</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4587,37 +4587,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D107" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E107" t="n">
-        <v>1200</v>
+        <v>520</v>
       </c>
       <c r="F107" t="n">
-        <v>38913.98</v>
+        <v>73251.91</v>
       </c>
       <c r="G107" t="n">
-        <v>572.76</v>
+        <v>3138.13</v>
       </c>
       <c r="H107" t="n">
-        <v>26591.22</v>
+        <v>35217.26</v>
       </c>
       <c r="I107" t="n">
-        <v>38341.22</v>
+        <v>70113.78</v>
       </c>
       <c r="J107" t="n">
-        <v>38341.22</v>
+        <v>70113.78</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4626,12 +4626,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
@@ -4641,22 +4641,22 @@
         <v>5</v>
       </c>
       <c r="E108" t="n">
-        <v>15400</v>
+        <v>520</v>
       </c>
       <c r="F108" t="n">
-        <v>138721.13</v>
+        <v>33296.32</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>88277.08</v>
+        <v>16007.85</v>
       </c>
       <c r="I108" t="n">
-        <v>138721.13</v>
+        <v>33296.32</v>
       </c>
       <c r="J108" t="n">
-        <v>138721.13</v>
+        <v>33296.32</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4665,37 +4665,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D109" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
-        <v>1200</v>
+        <v>1650</v>
       </c>
       <c r="F109" t="n">
-        <v>17295.1</v>
+        <v>42260.72</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>11818.32</v>
+        <v>21002.3</v>
       </c>
       <c r="I109" t="n">
-        <v>17295.1</v>
+        <v>42260.72</v>
       </c>
       <c r="J109" t="n">
-        <v>17295.1</v>
+        <v>42260.72</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4704,37 +4704,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D110" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E110" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F110" t="n">
-        <v>45399.64</v>
+        <v>91564.88</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>2353.6</v>
       </c>
       <c r="H110" t="n">
-        <v>31023.09</v>
+        <v>45078.1</v>
       </c>
       <c r="I110" t="n">
-        <v>45399.64</v>
+        <v>89211.28</v>
       </c>
       <c r="J110" t="n">
-        <v>45399.64</v>
+        <v>89211.28</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4743,37 +4743,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="D111" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E111" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F111" t="n">
-        <v>105932.5</v>
+        <v>166481.61</v>
       </c>
       <c r="G111" t="n">
-        <v>1559.18</v>
+        <v>7132.12</v>
       </c>
       <c r="H111" t="n">
-        <v>70621.66</v>
+        <v>81960.17999999999</v>
       </c>
       <c r="I111" t="n">
-        <v>104373.32</v>
+        <v>159349.49</v>
       </c>
       <c r="J111" t="n">
-        <v>104373.32</v>
+        <v>159349.49</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4782,37 +4782,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E112" t="n">
-        <v>21500</v>
+        <v>1950</v>
       </c>
       <c r="F112" t="n">
-        <v>154935.28</v>
+        <v>499444.83</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>8558.540000000001</v>
       </c>
       <c r="H112" t="n">
-        <v>102329.35</v>
+        <v>268931.83</v>
       </c>
       <c r="I112" t="n">
-        <v>154935.28</v>
+        <v>490886.29</v>
       </c>
       <c r="J112" t="n">
-        <v>154935.28</v>
+        <v>490886.29</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4821,37 +4821,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="D113" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E113" t="n">
-        <v>8900</v>
+        <v>390</v>
       </c>
       <c r="F113" t="n">
-        <v>224476</v>
+        <v>99888.97</v>
       </c>
       <c r="G113" t="n">
-        <v>4955.95</v>
+        <v>1711.71</v>
       </c>
       <c r="H113" t="n">
-        <v>148809.94</v>
+        <v>46102.6</v>
       </c>
       <c r="I113" t="n">
-        <v>219520.05</v>
+        <v>98177.25999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>219520.05</v>
+        <v>98177.25999999999</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4860,37 +4860,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="D114" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E114" t="n">
-        <v>1200</v>
+        <v>1650</v>
       </c>
       <c r="F114" t="n">
-        <v>54047.19</v>
+        <v>359216.09</v>
       </c>
       <c r="G114" t="n">
-        <v>795.5</v>
+        <v>15388.91</v>
       </c>
       <c r="H114" t="n">
-        <v>36932.25</v>
+        <v>178519.51</v>
       </c>
       <c r="I114" t="n">
-        <v>53251.69</v>
+        <v>343827.18</v>
       </c>
       <c r="J114" t="n">
-        <v>53251.69</v>
+        <v>343827.18</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4899,37 +4899,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D115" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E115" t="n">
-        <v>15400</v>
+        <v>950</v>
       </c>
       <c r="F115" t="n">
-        <v>582628.73</v>
+        <v>231153.31</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>3961.07</v>
       </c>
       <c r="H115" t="n">
-        <v>370763.74</v>
+        <v>111926.87</v>
       </c>
       <c r="I115" t="n">
-        <v>582628.73</v>
+        <v>227192.24</v>
       </c>
       <c r="J115" t="n">
-        <v>582628.73</v>
+        <v>227192.24</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4938,37 +4938,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="D116" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>4200</v>
+        <v>520</v>
       </c>
       <c r="F116" t="n">
-        <v>158898.74</v>
+        <v>6659.26</v>
       </c>
       <c r="G116" t="n">
-        <v>5846.91</v>
+        <v>114.11</v>
       </c>
       <c r="H116" t="n">
-        <v>105932.5</v>
+        <v>3201.57</v>
       </c>
       <c r="I116" t="n">
-        <v>153051.83</v>
+        <v>6545.15</v>
       </c>
       <c r="J116" t="n">
-        <v>153051.83</v>
+        <v>6545.15</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4977,37 +4977,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D117" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E117" t="n">
-        <v>1850</v>
+        <v>950</v>
       </c>
       <c r="F117" t="n">
-        <v>19997.46</v>
+        <v>48663.85</v>
       </c>
       <c r="G117" t="n">
-        <v>441.5</v>
+        <v>1250.86</v>
       </c>
       <c r="H117" t="n">
-        <v>13511.8</v>
+        <v>23563.55</v>
       </c>
       <c r="I117" t="n">
-        <v>19555.96</v>
+        <v>47412.99</v>
       </c>
       <c r="J117" t="n">
-        <v>19555.96</v>
+        <v>47412.99</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5016,37 +5016,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="D118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>8900</v>
+        <v>520</v>
       </c>
       <c r="F118" t="n">
-        <v>32068</v>
+        <v>6659.26</v>
       </c>
       <c r="G118" t="n">
-        <v>707.99</v>
+        <v>285.28</v>
       </c>
       <c r="H118" t="n">
-        <v>21258.56</v>
+        <v>3201.57</v>
       </c>
       <c r="I118" t="n">
-        <v>31360.01</v>
+        <v>6373.98</v>
       </c>
       <c r="J118" t="n">
-        <v>31360.01</v>
+        <v>6373.98</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5055,37 +5055,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="D119" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E119" t="n">
-        <v>21500</v>
+        <v>1950</v>
       </c>
       <c r="F119" t="n">
-        <v>232402.93</v>
+        <v>474472.58</v>
       </c>
       <c r="G119" t="n">
-        <v>3420.64</v>
+        <v>20326.53</v>
       </c>
       <c r="H119" t="n">
-        <v>153494.03</v>
+        <v>255485.24</v>
       </c>
       <c r="I119" t="n">
-        <v>228982.29</v>
+        <v>454146.05</v>
       </c>
       <c r="J119" t="n">
-        <v>228982.29</v>
+        <v>454146.05</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5094,37 +5094,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>1850</v>
+        <v>950</v>
       </c>
       <c r="F120" t="n">
-        <v>3332.91</v>
+        <v>24331.93</v>
       </c>
       <c r="G120" t="n">
-        <v>49.06</v>
+        <v>1042.39</v>
       </c>
       <c r="H120" t="n">
-        <v>2251.97</v>
+        <v>11781.78</v>
       </c>
       <c r="I120" t="n">
-        <v>3283.85</v>
+        <v>23289.54</v>
       </c>
       <c r="J120" t="n">
-        <v>3283.85</v>
+        <v>23289.54</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5133,37 +5133,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D121" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E121" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F121" t="n">
-        <v>83232.67999999999</v>
+        <v>141509.37</v>
       </c>
       <c r="G121" t="n">
-        <v>1225.07</v>
+        <v>6062.3</v>
       </c>
       <c r="H121" t="n">
-        <v>55488.45</v>
+        <v>69666.14999999999</v>
       </c>
       <c r="I121" t="n">
-        <v>82007.61</v>
+        <v>135447.07</v>
       </c>
       <c r="J121" t="n">
-        <v>82007.61</v>
+        <v>135447.07</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5172,37 +5172,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E122" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F122" t="n">
-        <v>193669.1</v>
+        <v>66592.64</v>
       </c>
       <c r="G122" t="n">
-        <v>7126.34</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>127911.69</v>
+        <v>32784.07</v>
       </c>
       <c r="I122" t="n">
-        <v>186542.76</v>
+        <v>66592.64</v>
       </c>
       <c r="J122" t="n">
-        <v>186542.76</v>
+        <v>66592.64</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5211,37 +5211,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="D123" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F123" t="n">
-        <v>194209.58</v>
+        <v>8324.08</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>213.96</v>
       </c>
       <c r="H123" t="n">
-        <v>123587.91</v>
+        <v>4098.01</v>
       </c>
       <c r="I123" t="n">
-        <v>194209.58</v>
+        <v>8110.12</v>
       </c>
       <c r="J123" t="n">
-        <v>194209.58</v>
+        <v>8110.12</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5250,37 +5250,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="D124" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E124" t="n">
-        <v>8900</v>
+        <v>390</v>
       </c>
       <c r="F124" t="n">
-        <v>384816.01</v>
+        <v>24972.24</v>
       </c>
       <c r="G124" t="n">
-        <v>8495.92</v>
+        <v>641.89</v>
       </c>
       <c r="H124" t="n">
-        <v>255102.75</v>
+        <v>11525.65</v>
       </c>
       <c r="I124" t="n">
-        <v>376320.09</v>
+        <v>24330.35</v>
       </c>
       <c r="J124" t="n">
-        <v>376320.09</v>
+        <v>24330.35</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5289,37 +5289,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>45906</v>
       </c>
       <c r="D125" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E125" t="n">
-        <v>15400</v>
+        <v>390</v>
       </c>
       <c r="F125" t="n">
-        <v>638117.1800000001</v>
+        <v>84905.62</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>3637.38</v>
       </c>
       <c r="H125" t="n">
-        <v>406074.57</v>
+        <v>39187.21</v>
       </c>
       <c r="I125" t="n">
-        <v>638117.1800000001</v>
+        <v>81268.24000000001</v>
       </c>
       <c r="J125" t="n">
-        <v>638117.1800000001</v>
+        <v>81268.24000000001</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5328,37 +5328,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="D126" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>650</v>
+        <v>520</v>
       </c>
       <c r="F126" t="n">
-        <v>11710.22</v>
+        <v>13318.53</v>
       </c>
       <c r="G126" t="n">
-        <v>430.89</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>7926.92</v>
+        <v>6403.14</v>
       </c>
       <c r="I126" t="n">
-        <v>11279.33</v>
+        <v>13318.53</v>
       </c>
       <c r="J126" t="n">
-        <v>11279.33</v>
+        <v>13318.53</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5367,37 +5367,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D127" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E127" t="n">
-        <v>1200</v>
+        <v>1650</v>
       </c>
       <c r="F127" t="n">
-        <v>12971.33</v>
+        <v>232433.94</v>
       </c>
       <c r="G127" t="n">
-        <v>477.3</v>
+        <v>5974.52</v>
       </c>
       <c r="H127" t="n">
-        <v>8863.74</v>
+        <v>115512.62</v>
       </c>
       <c r="I127" t="n">
-        <v>12494.03</v>
+        <v>226459.42</v>
       </c>
       <c r="J127" t="n">
-        <v>12494.03</v>
+        <v>226459.42</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5406,37 +5406,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="D128" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E128" t="n">
-        <v>2400</v>
+        <v>1950</v>
       </c>
       <c r="F128" t="n">
-        <v>60532.85</v>
+        <v>149833.45</v>
       </c>
       <c r="G128" t="n">
-        <v>2227.39</v>
+        <v>3851.34</v>
       </c>
       <c r="H128" t="n">
-        <v>37833.03</v>
+        <v>80679.55</v>
       </c>
       <c r="I128" t="n">
-        <v>58305.46</v>
+        <v>145982.11</v>
       </c>
       <c r="J128" t="n">
-        <v>58305.46</v>
+        <v>145982.11</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5445,37 +5445,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="D129" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E129" t="n">
-        <v>4200</v>
+        <v>1650</v>
       </c>
       <c r="F129" t="n">
-        <v>98365.89</v>
+        <v>253564.3</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>4345.11</v>
       </c>
       <c r="H129" t="n">
-        <v>65577.25999999999</v>
+        <v>126013.77</v>
       </c>
       <c r="I129" t="n">
-        <v>98365.89</v>
+        <v>249219.19</v>
       </c>
       <c r="J129" t="n">
-        <v>98365.89</v>
+        <v>249219.19</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5484,37 +5484,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="D130" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E130" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F130" t="n">
-        <v>256544</v>
+        <v>66592.64</v>
       </c>
       <c r="G130" t="n">
-        <v>3775.96</v>
+        <v>1141.14</v>
       </c>
       <c r="H130" t="n">
-        <v>170068.5</v>
+        <v>32784.07</v>
       </c>
       <c r="I130" t="n">
-        <v>252768.04</v>
+        <v>65451.5</v>
       </c>
       <c r="J130" t="n">
-        <v>252768.04</v>
+        <v>65451.5</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5523,37 +5523,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E131" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F131" t="n">
-        <v>2161.89</v>
+        <v>83240.8</v>
       </c>
       <c r="G131" t="n">
-        <v>31.82</v>
+        <v>1426.42</v>
       </c>
       <c r="H131" t="n">
-        <v>1477.29</v>
+        <v>40980.09</v>
       </c>
       <c r="I131" t="n">
-        <v>2130.07</v>
+        <v>81814.38</v>
       </c>
       <c r="J131" t="n">
-        <v>2130.07</v>
+        <v>81814.38</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5562,37 +5562,37 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v>45920</v>
       </c>
       <c r="D132" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E132" t="n">
-        <v>1200</v>
+        <v>950</v>
       </c>
       <c r="F132" t="n">
-        <v>32428.32</v>
+        <v>194655.42</v>
       </c>
       <c r="G132" t="n">
-        <v>477.3</v>
+        <v>3335.64</v>
       </c>
       <c r="H132" t="n">
-        <v>22159.35</v>
+        <v>94254.2</v>
       </c>
       <c r="I132" t="n">
-        <v>31951.02</v>
+        <v>191319.78</v>
       </c>
       <c r="J132" t="n">
-        <v>31951.02</v>
+        <v>191319.78</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5601,37 +5601,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="D133" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E133" t="n">
-        <v>15400</v>
+        <v>1950</v>
       </c>
       <c r="F133" t="n">
-        <v>527140.28</v>
+        <v>449500.34</v>
       </c>
       <c r="G133" t="n">
-        <v>19396.89</v>
+        <v>7702.69</v>
       </c>
       <c r="H133" t="n">
-        <v>335452.9</v>
+        <v>242038.65</v>
       </c>
       <c r="I133" t="n">
-        <v>507743.39</v>
+        <v>441797.65</v>
       </c>
       <c r="J133" t="n">
-        <v>507743.39</v>
+        <v>441797.65</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5640,37 +5640,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="D134" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E134" t="n">
-        <v>15400</v>
+        <v>3800</v>
       </c>
       <c r="F134" t="n">
-        <v>582628.73</v>
+        <v>924613.24</v>
       </c>
       <c r="G134" t="n">
-        <v>8575.469999999999</v>
+        <v>39610.68</v>
       </c>
       <c r="H134" t="n">
-        <v>370763.74</v>
+        <v>510970.48</v>
       </c>
       <c r="I134" t="n">
-        <v>574053.26</v>
+        <v>885002.5600000001</v>
       </c>
       <c r="J134" t="n">
-        <v>574053.26</v>
+        <v>885002.5600000001</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="D135" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E135" t="n">
-        <v>1200</v>
+        <v>390</v>
       </c>
       <c r="F135" t="n">
-        <v>4323.78</v>
+        <v>59933.38</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>2954.58</v>
+        <v>27661.56</v>
       </c>
       <c r="I135" t="n">
-        <v>4323.78</v>
+        <v>59933.38</v>
       </c>
       <c r="J135" t="n">
-        <v>4323.78</v>
+        <v>59933.38</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5718,37 +5718,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v>45928</v>
       </c>
       <c r="D136" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E136" t="n">
-        <v>15400</v>
+        <v>3800</v>
       </c>
       <c r="F136" t="n">
-        <v>166465.35</v>
+        <v>486638.55</v>
       </c>
       <c r="G136" t="n">
-        <v>3675.2</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>105932.5</v>
+        <v>268931.83</v>
       </c>
       <c r="I136" t="n">
-        <v>162790.15</v>
+        <v>486638.55</v>
       </c>
       <c r="J136" t="n">
-        <v>162790.15</v>
+        <v>486638.55</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -5757,37 +5757,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D137" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E137" t="n">
-        <v>15400</v>
+        <v>390</v>
       </c>
       <c r="F137" t="n">
-        <v>638117.1800000001</v>
+        <v>44950.03</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>1155.4</v>
       </c>
       <c r="H137" t="n">
-        <v>406074.57</v>
+        <v>20746.17</v>
       </c>
       <c r="I137" t="n">
-        <v>638117.1800000001</v>
+        <v>43794.63</v>
       </c>
       <c r="J137" t="n">
-        <v>638117.1800000001</v>
+        <v>43794.63</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -5796,37 +5796,37 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v>45933</v>
       </c>
       <c r="D138" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E138" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F138" t="n">
-        <v>332930.7</v>
+        <v>149833.45</v>
       </c>
       <c r="G138" t="n">
-        <v>12250.67</v>
+        <v>2567.56</v>
       </c>
       <c r="H138" t="n">
-        <v>211864.99</v>
+        <v>73764.16</v>
       </c>
       <c r="I138" t="n">
-        <v>320680.03</v>
+        <v>147265.89</v>
       </c>
       <c r="J138" t="n">
-        <v>320680.03</v>
+        <v>147265.89</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -5835,37 +5835,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="D139" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E139" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F139" t="n">
-        <v>10809.44</v>
+        <v>33296.32</v>
       </c>
       <c r="G139" t="n">
-        <v>238.65</v>
+        <v>1426.42</v>
       </c>
       <c r="H139" t="n">
-        <v>7386.45</v>
+        <v>16392.04</v>
       </c>
       <c r="I139" t="n">
-        <v>10570.79</v>
+        <v>31869.9</v>
       </c>
       <c r="J139" t="n">
-        <v>10570.79</v>
+        <v>31869.9</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -5874,37 +5874,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>45937</v>
       </c>
       <c r="D140" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F140" t="n">
-        <v>929611.7</v>
+        <v>16648.16</v>
       </c>
       <c r="G140" t="n">
-        <v>34206.41</v>
+        <v>713.21</v>
       </c>
       <c r="H140" t="n">
-        <v>613976.1</v>
+        <v>8196.02</v>
       </c>
       <c r="I140" t="n">
-        <v>895405.29</v>
+        <v>15934.95</v>
       </c>
       <c r="J140" t="n">
-        <v>895405.29</v>
+        <v>15934.95</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -5913,37 +5913,37 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="D141" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E141" t="n">
-        <v>2400</v>
+        <v>950</v>
       </c>
       <c r="F141" t="n">
-        <v>99446.83</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="G141" t="n">
-        <v>3659.29</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>62154.27</v>
+        <v>47127.1</v>
       </c>
       <c r="I141" t="n">
-        <v>95787.53999999999</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="J141" t="n">
-        <v>95787.53999999999</v>
+        <v>97327.71000000001</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -5952,37 +5952,37 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="D142" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E142" t="n">
-        <v>21500</v>
+        <v>390</v>
       </c>
       <c r="F142" t="n">
-        <v>968345.52</v>
+        <v>54938.93</v>
       </c>
       <c r="G142" t="n">
-        <v>35631.68</v>
+        <v>1412.16</v>
       </c>
       <c r="H142" t="n">
-        <v>639558.4399999999</v>
+        <v>25356.43</v>
       </c>
       <c r="I142" t="n">
-        <v>932713.84</v>
+        <v>53526.77</v>
       </c>
       <c r="J142" t="n">
-        <v>932713.84</v>
+        <v>53526.77</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -5991,37 +5991,37 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="D143" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E143" t="n">
-        <v>1200</v>
+        <v>950</v>
       </c>
       <c r="F143" t="n">
-        <v>54047.19</v>
+        <v>60829.82</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>36932.25</v>
+        <v>29454.44</v>
       </c>
       <c r="I143" t="n">
-        <v>54047.19</v>
+        <v>60829.82</v>
       </c>
       <c r="J143" t="n">
-        <v>54047.19</v>
+        <v>60829.82</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6030,37 +6030,37 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E144" t="n">
-        <v>4200</v>
+        <v>390</v>
       </c>
       <c r="F144" t="n">
-        <v>128632.32</v>
+        <v>79911.17</v>
       </c>
       <c r="G144" t="n">
-        <v>2839.93</v>
+        <v>2054.05</v>
       </c>
       <c r="H144" t="n">
-        <v>85754.88</v>
+        <v>36882.08</v>
       </c>
       <c r="I144" t="n">
-        <v>125792.39</v>
+        <v>77857.12</v>
       </c>
       <c r="J144" t="n">
-        <v>125792.39</v>
+        <v>77857.12</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6069,37 +6069,37 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D145" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E145" t="n">
-        <v>650</v>
+        <v>520</v>
       </c>
       <c r="F145" t="n">
-        <v>3513.07</v>
+        <v>66592.64</v>
       </c>
       <c r="G145" t="n">
-        <v>129.27</v>
+        <v>1141.14</v>
       </c>
       <c r="H145" t="n">
-        <v>2378.08</v>
+        <v>32015.69</v>
       </c>
       <c r="I145" t="n">
-        <v>3383.8</v>
+        <v>65451.5</v>
       </c>
       <c r="J145" t="n">
-        <v>3383.8</v>
+        <v>65451.5</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6108,37 +6108,37 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v>45949</v>
       </c>
       <c r="D146" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
-        <v>1850</v>
+        <v>950</v>
       </c>
       <c r="F146" t="n">
-        <v>59992.38</v>
+        <v>24331.93</v>
       </c>
       <c r="G146" t="n">
-        <v>2207.51</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>40535.39</v>
+        <v>11781.78</v>
       </c>
       <c r="I146" t="n">
-        <v>57784.87</v>
+        <v>24331.93</v>
       </c>
       <c r="J146" t="n">
-        <v>57784.87</v>
+        <v>24331.93</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6147,37 +6147,37 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D147" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E147" t="n">
-        <v>8900</v>
+        <v>1650</v>
       </c>
       <c r="F147" t="n">
-        <v>96204</v>
+        <v>42260.72</v>
       </c>
       <c r="G147" t="n">
-        <v>1415.99</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>63775.69</v>
+        <v>21002.3</v>
       </c>
       <c r="I147" t="n">
-        <v>94788.00999999999</v>
+        <v>42260.72</v>
       </c>
       <c r="J147" t="n">
-        <v>94788.00999999999</v>
+        <v>42260.72</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -6186,37 +6186,37 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D148" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E148" t="n">
-        <v>21500</v>
+        <v>520</v>
       </c>
       <c r="F148" t="n">
-        <v>154935.28</v>
+        <v>39955.59</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>102329.35</v>
+        <v>19209.42</v>
       </c>
       <c r="I148" t="n">
-        <v>154935.28</v>
+        <v>39955.59</v>
       </c>
       <c r="J148" t="n">
-        <v>154935.28</v>
+        <v>39955.59</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -6225,37 +6225,37 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="D149" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E149" t="n">
-        <v>21500</v>
+        <v>520</v>
       </c>
       <c r="F149" t="n">
-        <v>116201.46</v>
+        <v>106548.23</v>
       </c>
       <c r="G149" t="n">
-        <v>4275.8</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>76747.00999999999</v>
+        <v>51225.11</v>
       </c>
       <c r="I149" t="n">
-        <v>111925.66</v>
+        <v>106548.23</v>
       </c>
       <c r="J149" t="n">
-        <v>111925.66</v>
+        <v>106548.23</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -6264,37 +6264,37 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="D150" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>1850</v>
+        <v>3800</v>
       </c>
       <c r="F150" t="n">
-        <v>49993.65</v>
+        <v>48663.85</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>833.91</v>
       </c>
       <c r="H150" t="n">
-        <v>33779.49</v>
+        <v>26893.18</v>
       </c>
       <c r="I150" t="n">
-        <v>49993.65</v>
+        <v>47829.94</v>
       </c>
       <c r="J150" t="n">
-        <v>49993.65</v>
+        <v>47829.94</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -6303,37 +6303,37 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E151" t="n">
-        <v>2400</v>
+        <v>1950</v>
       </c>
       <c r="F151" t="n">
-        <v>64856.63</v>
+        <v>249722.41</v>
       </c>
       <c r="G151" t="n">
-        <v>2386.49</v>
+        <v>6418.91</v>
       </c>
       <c r="H151" t="n">
-        <v>40535.39</v>
+        <v>134465.91</v>
       </c>
       <c r="I151" t="n">
-        <v>62470.14</v>
+        <v>243303.5</v>
       </c>
       <c r="J151" t="n">
-        <v>62470.14</v>
+        <v>243303.5</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -6342,37 +6342,37 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D152" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E152" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F152" t="n">
-        <v>852144.0600000001</v>
+        <v>141509.37</v>
       </c>
       <c r="G152" t="n">
-        <v>12542.35</v>
+        <v>3637.38</v>
       </c>
       <c r="H152" t="n">
-        <v>562811.4300000001</v>
+        <v>69666.14999999999</v>
       </c>
       <c r="I152" t="n">
-        <v>839601.71</v>
+        <v>137871.99</v>
       </c>
       <c r="J152" t="n">
-        <v>839601.71</v>
+        <v>137871.99</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
@@ -6381,37 +6381,37 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v>45963</v>
       </c>
       <c r="D153" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E153" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F153" t="n">
-        <v>43327.83</v>
+        <v>33296.32</v>
       </c>
       <c r="G153" t="n">
-        <v>637.72</v>
+        <v>570.5700000000001</v>
       </c>
       <c r="H153" t="n">
-        <v>29275.56</v>
+        <v>16392.04</v>
       </c>
       <c r="I153" t="n">
-        <v>42690.11</v>
+        <v>32725.75</v>
       </c>
       <c r="J153" t="n">
-        <v>42690.11</v>
+        <v>32725.75</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -6420,37 +6420,37 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D154" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E154" t="n">
-        <v>1850</v>
+        <v>950</v>
       </c>
       <c r="F154" t="n">
-        <v>79989.84</v>
+        <v>182489.46</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>3127.16</v>
       </c>
       <c r="H154" t="n">
-        <v>54047.19</v>
+        <v>88363.32000000001</v>
       </c>
       <c r="I154" t="n">
-        <v>79989.84</v>
+        <v>179362.3</v>
       </c>
       <c r="J154" t="n">
-        <v>79989.84</v>
+        <v>179362.3</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -6459,37 +6459,37 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E155" t="n">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="F155" t="n">
-        <v>15133.21</v>
+        <v>535302.4</v>
       </c>
       <c r="G155" t="n">
-        <v>334.11</v>
+        <v>9173</v>
       </c>
       <c r="H155" t="n">
-        <v>10088.81</v>
+        <v>295825.01</v>
       </c>
       <c r="I155" t="n">
-        <v>14799.1</v>
+        <v>526129.4</v>
       </c>
       <c r="J155" t="n">
-        <v>14799.1</v>
+        <v>526129.4</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
@@ -6498,37 +6498,37 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v>45969</v>
       </c>
       <c r="D156" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E156" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F156" t="n">
-        <v>136198.92</v>
+        <v>166481.61</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>4279.27</v>
       </c>
       <c r="H156" t="n">
-        <v>90799.28</v>
+        <v>81960.17999999999</v>
       </c>
       <c r="I156" t="n">
-        <v>136198.92</v>
+        <v>162202.34</v>
       </c>
       <c r="J156" t="n">
-        <v>136198.92</v>
+        <v>162202.34</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -6537,37 +6537,37 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D157" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E157" t="n">
-        <v>4200</v>
+        <v>1650</v>
       </c>
       <c r="F157" t="n">
-        <v>121065.71</v>
+        <v>232433.94</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>80710.47</v>
+        <v>115512.62</v>
       </c>
       <c r="I157" t="n">
-        <v>121065.71</v>
+        <v>232433.94</v>
       </c>
       <c r="J157" t="n">
-        <v>121065.71</v>
+        <v>232433.94</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -6576,37 +6576,37 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="D158" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E158" t="n">
-        <v>2400</v>
+        <v>950</v>
       </c>
       <c r="F158" t="n">
-        <v>25942.65</v>
+        <v>48663.85</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>16214.16</v>
+        <v>23563.55</v>
       </c>
       <c r="I158" t="n">
-        <v>25942.65</v>
+        <v>48663.85</v>
       </c>
       <c r="J158" t="n">
-        <v>25942.65</v>
+        <v>48663.85</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -6615,37 +6615,37 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="D159" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E159" t="n">
-        <v>2400</v>
+        <v>390</v>
       </c>
       <c r="F159" t="n">
-        <v>51885.3</v>
+        <v>54938.93</v>
       </c>
       <c r="G159" t="n">
-        <v>1145.52</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>32428.32</v>
+        <v>25356.43</v>
       </c>
       <c r="I159" t="n">
-        <v>50739.78</v>
+        <v>54938.93</v>
       </c>
       <c r="J159" t="n">
-        <v>50739.78</v>
+        <v>54938.93</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -6654,12 +6654,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
@@ -6669,22 +6669,22 @@
         <v>13</v>
       </c>
       <c r="E160" t="n">
-        <v>2400</v>
+        <v>1950</v>
       </c>
       <c r="F160" t="n">
-        <v>56209.08</v>
+        <v>324639.14</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>35130.67</v>
+        <v>174805.69</v>
       </c>
       <c r="I160" t="n">
-        <v>56209.08</v>
+        <v>324639.14</v>
       </c>
       <c r="J160" t="n">
-        <v>56209.08</v>
+        <v>324639.14</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -6693,37 +6693,37 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="D161" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E161" t="n">
-        <v>8900</v>
+        <v>520</v>
       </c>
       <c r="F161" t="n">
-        <v>336714.01</v>
+        <v>59933.38</v>
       </c>
       <c r="G161" t="n">
-        <v>4955.95</v>
+        <v>1027.02</v>
       </c>
       <c r="H161" t="n">
-        <v>223214.9</v>
+        <v>28814.12</v>
       </c>
       <c r="I161" t="n">
-        <v>331758.06</v>
+        <v>58906.36</v>
       </c>
       <c r="J161" t="n">
-        <v>331758.06</v>
+        <v>58906.36</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -6732,37 +6732,37 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D162" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E162" t="n">
-        <v>8900</v>
+        <v>1650</v>
       </c>
       <c r="F162" t="n">
-        <v>288612</v>
+        <v>401476.8</v>
       </c>
       <c r="G162" t="n">
-        <v>6371.94</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>191327.06</v>
+        <v>199521.8</v>
       </c>
       <c r="I162" t="n">
-        <v>282240.06</v>
+        <v>401476.8</v>
       </c>
       <c r="J162" t="n">
-        <v>282240.06</v>
+        <v>401476.8</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
@@ -6771,37 +6771,37 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="D163" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E163" t="n">
-        <v>8900</v>
+        <v>950</v>
       </c>
       <c r="F163" t="n">
-        <v>384816.01</v>
+        <v>145991.56</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>255102.75</v>
+        <v>70690.64999999999</v>
       </c>
       <c r="I163" t="n">
-        <v>384816.01</v>
+        <v>145991.56</v>
       </c>
       <c r="J163" t="n">
-        <v>384816.01</v>
+        <v>145991.56</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -6810,37 +6810,37 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="D164" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E164" t="n">
-        <v>1850</v>
+        <v>950</v>
       </c>
       <c r="F164" t="n">
-        <v>83322.75</v>
+        <v>48663.85</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>1250.86</v>
       </c>
       <c r="H164" t="n">
-        <v>56299.16</v>
+        <v>23563.55</v>
       </c>
       <c r="I164" t="n">
-        <v>83322.75</v>
+        <v>47412.99</v>
       </c>
       <c r="J164" t="n">
-        <v>83322.75</v>
+        <v>47412.99</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -6849,37 +6849,37 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Slim Fit Chino Pantolon</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D165" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E165" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F165" t="n">
-        <v>852144.0600000001</v>
+        <v>108213.05</v>
       </c>
       <c r="G165" t="n">
-        <v>31355.88</v>
+        <v>4635.88</v>
       </c>
       <c r="H165" t="n">
-        <v>562811.4300000001</v>
+        <v>53274.11</v>
       </c>
       <c r="I165" t="n">
-        <v>820788.1800000001</v>
+        <v>103577.17</v>
       </c>
       <c r="J165" t="n">
-        <v>820788.1800000001</v>
+        <v>103577.17</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -6888,37 +6888,37 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Stratejik Ortak E - ModaStyle</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="D166" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E166" t="n">
-        <v>2400</v>
+        <v>950</v>
       </c>
       <c r="F166" t="n">
-        <v>34590.2</v>
+        <v>48663.85</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>833.91</v>
       </c>
       <c r="H166" t="n">
-        <v>21618.88</v>
+        <v>23563.55</v>
       </c>
       <c r="I166" t="n">
-        <v>34590.2</v>
+        <v>47829.94</v>
       </c>
       <c r="J166" t="n">
-        <v>34590.2</v>
+        <v>47829.94</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -6927,37 +6927,37 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="D167" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E167" t="n">
-        <v>650</v>
+        <v>1650</v>
       </c>
       <c r="F167" t="n">
-        <v>5855.11</v>
+        <v>169042.86</v>
       </c>
       <c r="G167" t="n">
-        <v>86.18000000000001</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>3963.46</v>
+        <v>84009.17999999999</v>
       </c>
       <c r="I167" t="n">
-        <v>5768.93</v>
+        <v>169042.86</v>
       </c>
       <c r="J167" t="n">
-        <v>5768.93</v>
+        <v>169042.86</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -6966,37 +6966,37 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="D168" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E168" t="n">
-        <v>4200</v>
+        <v>390</v>
       </c>
       <c r="F168" t="n">
-        <v>15133.21</v>
+        <v>24972.24</v>
       </c>
       <c r="G168" t="n">
-        <v>334.11</v>
+        <v>641.89</v>
       </c>
       <c r="H168" t="n">
-        <v>10088.81</v>
+        <v>11525.65</v>
       </c>
       <c r="I168" t="n">
-        <v>14799.1</v>
+        <v>24330.35</v>
       </c>
       <c r="J168" t="n">
-        <v>14799.1</v>
+        <v>24330.35</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -7005,37 +7005,37 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="D169" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E169" t="n">
-        <v>1850</v>
+        <v>390</v>
       </c>
       <c r="F169" t="n">
-        <v>26663.28</v>
+        <v>89900.07000000001</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>2310.81</v>
       </c>
       <c r="H169" t="n">
-        <v>18015.73</v>
+        <v>41492.34</v>
       </c>
       <c r="I169" t="n">
-        <v>26663.28</v>
+        <v>87589.25999999999</v>
       </c>
       <c r="J169" t="n">
-        <v>26663.28</v>
+        <v>87589.25999999999</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
@@ -7044,37 +7044,37 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v>45997</v>
       </c>
       <c r="D170" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E170" t="n">
-        <v>4200</v>
+        <v>520</v>
       </c>
       <c r="F170" t="n">
-        <v>151332.14</v>
+        <v>53274.11</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>2282.28</v>
       </c>
       <c r="H170" t="n">
-        <v>100888.09</v>
+        <v>25612.56</v>
       </c>
       <c r="I170" t="n">
-        <v>151332.14</v>
+        <v>50991.83</v>
       </c>
       <c r="J170" t="n">
-        <v>151332.14</v>
+        <v>50991.83</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
@@ -7083,37 +7083,37 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="D171" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E171" t="n">
-        <v>1850</v>
+        <v>1650</v>
       </c>
       <c r="F171" t="n">
-        <v>26663.28</v>
+        <v>316955.37</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>13578.45</v>
       </c>
       <c r="H171" t="n">
-        <v>18015.73</v>
+        <v>157517.21</v>
       </c>
       <c r="I171" t="n">
-        <v>26663.28</v>
+        <v>303376.92</v>
       </c>
       <c r="J171" t="n">
-        <v>26663.28</v>
+        <v>303376.92</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -7122,37 +7122,37 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Toptan Müşteri F - ModaStyle</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="D172" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E172" t="n">
-        <v>21500</v>
+        <v>3800</v>
       </c>
       <c r="F172" t="n">
-        <v>309870.57</v>
+        <v>924613.24</v>
       </c>
       <c r="G172" t="n">
-        <v>11402.14</v>
+        <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>204658.7</v>
+        <v>510970.48</v>
       </c>
       <c r="I172" t="n">
-        <v>298468.43</v>
+        <v>924613.24</v>
       </c>
       <c r="J172" t="n">
-        <v>298468.43</v>
+        <v>924613.24</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -7161,37 +7161,37 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Polar Fermuarlı Yelek</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="D173" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E173" t="n">
-        <v>1850</v>
+        <v>520</v>
       </c>
       <c r="F173" t="n">
-        <v>16664.55</v>
+        <v>119866.76</v>
       </c>
       <c r="G173" t="n">
-        <v>613.2</v>
+        <v>5135.12</v>
       </c>
       <c r="H173" t="n">
-        <v>11259.83</v>
+        <v>57628.25</v>
       </c>
       <c r="I173" t="n">
-        <v>16051.35</v>
+        <v>114731.64</v>
       </c>
       <c r="J173" t="n">
-        <v>16051.35</v>
+        <v>114731.64</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -7200,313 +7200,313 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kurumsal Müşteri D - ModaStyle</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Kruvaze Blazer Ceket</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v>46005</v>
       </c>
       <c r="D174" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E174" t="n">
-        <v>1200</v>
+        <v>1650</v>
       </c>
       <c r="F174" t="n">
-        <v>51885.3</v>
+        <v>380346.44</v>
       </c>
       <c r="G174" t="n">
-        <v>1909.2</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>35454.96</v>
+        <v>189020.66</v>
       </c>
       <c r="I174" t="n">
-        <v>49976.1</v>
+        <v>380346.44</v>
       </c>
       <c r="J174" t="n">
-        <v>14992.83</v>
+        <v>190173.22</v>
       </c>
       <c r="K174" t="n">
-        <v>34983.27</v>
+        <v>190173.22</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bölge Bayi C - ModaStyle</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="D175" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E175" t="n">
-        <v>650</v>
+        <v>1950</v>
       </c>
       <c r="F175" t="n">
-        <v>9368.18</v>
+        <v>424528.1</v>
       </c>
       <c r="G175" t="n">
-        <v>137.89</v>
+        <v>10912.14</v>
       </c>
       <c r="H175" t="n">
-        <v>6341.54</v>
+        <v>228592.05</v>
       </c>
       <c r="I175" t="n">
-        <v>9230.290000000001</v>
+        <v>413615.96</v>
       </c>
       <c r="J175" t="n">
-        <v>2769.09</v>
+        <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>6461.2</v>
+        <v>413615.96</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu B - ModaStyle</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D176" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E176" t="n">
-        <v>8900</v>
+        <v>950</v>
       </c>
       <c r="F176" t="n">
-        <v>352748.01</v>
+        <v>85161.75</v>
       </c>
       <c r="G176" t="n">
-        <v>12979.88</v>
+        <v>3648.35</v>
       </c>
       <c r="H176" t="n">
-        <v>233844.18</v>
+        <v>41236.21</v>
       </c>
       <c r="I176" t="n">
-        <v>339768.13</v>
+        <v>81513.39999999999</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>339768.13</v>
+        <v>81513.39999999999</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Kaşmir Karışımlı Palto</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="D177" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E177" t="n">
-        <v>2400</v>
+        <v>3800</v>
       </c>
       <c r="F177" t="n">
-        <v>43237.75</v>
+        <v>827285.53</v>
       </c>
       <c r="G177" t="n">
-        <v>636.4</v>
+        <v>21264.68</v>
       </c>
       <c r="H177" t="n">
-        <v>27023.6</v>
+        <v>457184.11</v>
       </c>
       <c r="I177" t="n">
-        <v>42601.35</v>
+        <v>806020.85</v>
       </c>
       <c r="J177" t="n">
-        <v>21300.67</v>
+        <v>241806.25</v>
       </c>
       <c r="K177" t="n">
-        <v>21300.68</v>
+        <v>564214.6</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Müşteri Grubu A - ModaStyle</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="D178" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E178" t="n">
-        <v>8900</v>
+        <v>390</v>
       </c>
       <c r="F178" t="n">
-        <v>336714.01</v>
+        <v>24972.24</v>
       </c>
       <c r="G178" t="n">
-        <v>7433.93</v>
+        <v>1069.82</v>
       </c>
       <c r="H178" t="n">
-        <v>223214.9</v>
+        <v>11525.65</v>
       </c>
       <c r="I178" t="n">
-        <v>329280.08</v>
+        <v>23902.42</v>
       </c>
       <c r="J178" t="n">
-        <v>98784.02</v>
+        <v>7170.73</v>
       </c>
       <c r="K178" t="n">
-        <v>230496.06</v>
+        <v>16731.69</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Basic Pamuklu T-Shirt 3'lü</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E179" t="n">
-        <v>21500</v>
+        <v>390</v>
       </c>
       <c r="F179" t="n">
-        <v>77467.64</v>
+        <v>94894.52</v>
       </c>
       <c r="G179" t="n">
-        <v>1140.21</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>51164.68</v>
+        <v>43797.47</v>
       </c>
       <c r="I179" t="n">
-        <v>76327.42999999999</v>
+        <v>94894.52</v>
       </c>
       <c r="J179" t="n">
-        <v>0</v>
+        <v>47447.26</v>
       </c>
       <c r="K179" t="n">
-        <v>76327.42999999999</v>
+        <v>47447.26</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - ModaStyle</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Omuz Çantası Vizon</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="D180" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E180" t="n">
-        <v>2400</v>
+        <v>950</v>
       </c>
       <c r="F180" t="n">
-        <v>73504.17999999999</v>
+        <v>121659.64</v>
       </c>
       <c r="G180" t="n">
-        <v>1081.88</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>45940.11</v>
+        <v>58908.88</v>
       </c>
       <c r="I180" t="n">
-        <v>72422.3</v>
+        <v>121659.64</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>72422.3</v>
+        <v>121659.64</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ticari Kanal G - ModaStyle</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Deri Chelsea Bot</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="D181" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>2400</v>
+        <v>1950</v>
       </c>
       <c r="F181" t="n">
-        <v>60532.85</v>
+        <v>24972.24</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>37833.03</v>
+        <v>13446.59</v>
       </c>
       <c r="I181" t="n">
-        <v>60532.85</v>
+        <v>24972.24</v>
       </c>
       <c r="J181" t="n">
-        <v>18159.85</v>
+        <v>12486.12</v>
       </c>
       <c r="K181" t="n">
-        <v>42373</v>
+        <v>12486.12</v>
       </c>
     </row>
   </sheetData>
